--- a/data/macro/nominal_gdp_growth_2016-2030.xlsx
+++ b/data/macro/nominal_gdp_growth_2016-2030.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a01403564_tec_mx/Documents/Escritorio/CFA-Research/.claude/worktrees/dcf-balance-general-dd4b56/data/macro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_024369B487A439F9D0E0A672B27F640747C83C20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD3AA599-1108-4511-B5AA-CC0997D93AD1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_60CF54336E4F33E546B2D16F98E4A86CB6FE0779" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Organic_pass" sheetId="11" r:id="rId11"/>
     <sheet name="Cross_check_history" sheetId="12" r:id="rId12"/>
     <sheet name="Regional_FX" sheetId="13" r:id="rId13"/>
+    <sheet name="PPP_terminal" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$1:$K$641</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5434" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5568" uniqueCount="440">
   <si>
     <t>Nominal GDP growth, local currency, 2016-2030 (Grupo Bimbo regions)</t>
   </si>
@@ -1351,6 +1352,24 @@
   <si>
     <t>Limits: weights are GDP, not Bimbo sales by country (not disclosed): China is the largest EAA weight and Brazil the largest Latin America weight. Annual-average FX; Bimbo translates hyperinflationary Argentina at the closing rate (IAS 29, EEFF25 p.23, p.26). Capital IQ FX forecasts [sourced] via sheet FX.</t>
   </si>
+  <si>
+    <t>Terminal FX, local currency to USD, by purchasing power parity 2030 [calc]: PPP ratio = (1 + US CPI) / (1 + currency CPI); below 1 = the currency loses vs USD. CPI from IAS29_test (Capital IQ) [sourced]. USD countries = 1; EUR = GDP-weighted CPI of the euro countries</t>
+  </si>
+  <si>
+    <t>CPI 2030</t>
+  </si>
+  <si>
+    <t>currency CPI 2030</t>
+  </si>
+  <si>
+    <t>PPP ratio 2030</t>
+  </si>
+  <si>
+    <t>Region factor 2030, local currency to USD, PPP [calc] = sum(weight x (1 + GDP growth) x PPP ratio) / sum(weight x (1 + GDP growth)), as Regional_FX</t>
+  </si>
+  <si>
+    <t>Mexico and North America = 1 here: the USD/MXN PPP step is applied in the statements workbook ((1 + Mexico CPI) / (1 + US CPI)). Limits: GDP weights, not Bimbo sales by country; annual-average CPI; one year (2030) as the long-run proxy.</t>
+  </si>
 </sst>
 </file>
 
@@ -1374,13 +1393,11 @@
       <b/>
       <sz val="13"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4859,6 +4876,1016 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" s="4">
+        <f>IAS29_test!R3</f>
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="E3" s="4">
+        <f>D3</f>
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="F3" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E3),0)</f>
+        <v>0.99522184300341288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" s="4">
+        <f>IAS29_test!R4</f>
+        <v>2.06E-2</v>
+      </c>
+      <c r="E4" s="4">
+        <f>IAS29_test!R4</f>
+        <v>2.06E-2</v>
+      </c>
+      <c r="F4" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E4),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="4">
+        <f>IAS29_test!R5</f>
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" ref="E5:E10" si="0">D5</f>
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="F5" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E5),0)</f>
+        <v>1.0019634792852936</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="4">
+        <f>IAS29_test!R6</f>
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="0"/>
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="F6" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E6),0)</f>
+        <v>0.95303016154636289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="4">
+        <f>IAS29_test!R7</f>
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="0"/>
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="F7" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E7),0)</f>
+        <v>0.9888576688305396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="4">
+        <f>IAS29_test!R8</f>
+        <v>3.09E-2</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.09E-2</v>
+      </c>
+      <c r="F8" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E8),0)</f>
+        <v>0.99000873023571634</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="4">
+        <f>IAS29_test!R9</f>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F9" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E9),0)</f>
+        <v>0.98799612778315593</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="4">
+        <f>IAS29_test!R10</f>
+        <v>2.18E-2</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>2.18E-2</v>
+      </c>
+      <c r="F10" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E10),0)</f>
+        <v>0.99882560187903691</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="4">
+        <f>IAS29_test!R11</f>
+        <v>2.07E-2</v>
+      </c>
+      <c r="E11" s="4">
+        <f>IAS29_test!R4</f>
+        <v>2.06E-2</v>
+      </c>
+      <c r="F11" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E11),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="4">
+        <f>IAS29_test!R12</f>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="E12" s="4">
+        <f>IAS29_test!R4</f>
+        <v>2.06E-2</v>
+      </c>
+      <c r="F12" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E12),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" s="4">
+        <f>IAS29_test!R13</f>
+        <v>3.04E-2</v>
+      </c>
+      <c r="E13" s="4">
+        <f>D13</f>
+        <v>3.04E-2</v>
+      </c>
+      <c r="F13" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E13),0)</f>
+        <v>0.99048913043478259</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D14" s="4">
+        <f>IAS29_test!R14</f>
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="E14" s="4">
+        <f>D14</f>
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="F14" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E14),0)</f>
+        <v>0.98456492378931115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="4">
+        <f>IAS29_test!R15</f>
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="E15" s="4">
+        <f>D15</f>
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="F15" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E15),0)</f>
+        <v>0.98751814223512324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" s="4">
+        <f>IAS29_test!R16</f>
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="E16" s="4">
+        <f>IAS29_test!R4</f>
+        <v>2.06E-2</v>
+      </c>
+      <c r="F16" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E16),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>227</v>
+      </c>
+      <c r="D17" s="4">
+        <f>IAS29_test!R17</f>
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" ref="E17:E24" si="1">D17</f>
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="F17" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E17),0)</f>
+        <v>0.98732707748863291</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>225</v>
+      </c>
+      <c r="D18" s="4">
+        <f>IAS29_test!R18</f>
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="F18" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E18),0)</f>
+        <v>0.99309136907657869</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>242</v>
+      </c>
+      <c r="D19" s="4">
+        <f>IAS29_test!R19</f>
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="1"/>
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="F19" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E19),0)</f>
+        <v>0.98981670061099802</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="4">
+        <f>IAS29_test!R20</f>
+        <v>0.1177</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="1"/>
+        <v>0.1177</v>
+      </c>
+      <c r="F20" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E20),0)</f>
+        <v>0.91312516775521158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D21" s="4">
+        <f>IAS29_test!R21</f>
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="1"/>
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="F21" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E21),0)</f>
+        <v>0.99931459904043851</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="4">
+        <f>IAS29_test!R22</f>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="1"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="F22" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E22),0)</f>
+        <v>1.0130024813895782</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" s="4">
+        <f>IAS29_test!R23</f>
+        <v>2.98E-2</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="1"/>
+        <v>2.98E-2</v>
+      </c>
+      <c r="F23" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E23),0)</f>
+        <v>0.99106622645173814</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" s="4">
+        <f>IAS29_test!R24</f>
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="1"/>
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="F24" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E24),0)</f>
+        <v>0.99125874125874114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="4">
+        <f>IAS29_test!R25</f>
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="E25" s="4">
+        <f>(Regional_agg!S25*IAS29_test!R25+Regional_agg!S26*IAS29_test!R26+Regional_agg!S27*IAS29_test!R27+Regional_agg!S39*IAS29_test!R39+Regional_agg!S40*IAS29_test!R40+Regional_agg!S41*IAS29_test!R41+Regional_agg!S42*IAS29_test!R42)/(Regional_agg!S25+Regional_agg!S26+Regional_agg!S27+Regional_agg!S39+Regional_agg!S40+Regional_agg!S41+Regional_agg!S42)</f>
+        <v>1.8992714458767924E-2</v>
+      </c>
+      <c r="F25" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E25),0)</f>
+        <v>1.0015773278046309</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="4">
+        <f>IAS29_test!R26</f>
+        <v>2.01E-2</v>
+      </c>
+      <c r="E26" s="4">
+        <f>(Regional_agg!S25*IAS29_test!R25+Regional_agg!S26*IAS29_test!R26+Regional_agg!S27*IAS29_test!R27+Regional_agg!S39*IAS29_test!R39+Regional_agg!S40*IAS29_test!R40+Regional_agg!S41*IAS29_test!R41+Regional_agg!S42*IAS29_test!R42)/(Regional_agg!S25+Regional_agg!S26+Regional_agg!S27+Regional_agg!S39+Regional_agg!S40+Regional_agg!S41+Regional_agg!S42)</f>
+        <v>1.8992714458767924E-2</v>
+      </c>
+      <c r="F26" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E26),0)</f>
+        <v>1.0015773278046309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="4">
+        <f>IAS29_test!R27</f>
+        <v>2.64E-2</v>
+      </c>
+      <c r="E27" s="4">
+        <f>(Regional_agg!S25*IAS29_test!R25+Regional_agg!S26*IAS29_test!R26+Regional_agg!S27*IAS29_test!R27+Regional_agg!S39*IAS29_test!R39+Regional_agg!S40*IAS29_test!R40+Regional_agg!S41*IAS29_test!R41+Regional_agg!S42*IAS29_test!R42)/(Regional_agg!S25+Regional_agg!S26+Regional_agg!S27+Regional_agg!S39+Regional_agg!S40+Regional_agg!S41+Regional_agg!S42)</f>
+        <v>1.8992714458767924E-2</v>
+      </c>
+      <c r="F27" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E27),0)</f>
+        <v>1.0015773278046309</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="4">
+        <f>IAS29_test!R28</f>
+        <v>2.29E-2</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" ref="E28:E38" si="2">D28</f>
+        <v>2.29E-2</v>
+      </c>
+      <c r="F28" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E28),0)</f>
+        <v>0.99775149085932158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
+        <v>233</v>
+      </c>
+      <c r="D29" s="4">
+        <f>IAS29_test!R29</f>
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="E29" s="4">
+        <f t="shared" si="2"/>
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="F29" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E29),0)</f>
+        <v>0.96959908797263916</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>239</v>
+      </c>
+      <c r="D30" s="4">
+        <f>IAS29_test!R30</f>
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="2"/>
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="F30" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E30),0)</f>
+        <v>0.95267432091851023</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>237</v>
+      </c>
+      <c r="D31" s="4">
+        <f>IAS29_test!R31</f>
+        <v>0.1077</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" si="2"/>
+        <v>0.1077</v>
+      </c>
+      <c r="F31" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E31),0)</f>
+        <v>0.92136860160693335</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="4">
+        <f>IAS29_test!R32</f>
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="2"/>
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="F32" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E32),0)</f>
+        <v>0.95839984975115033</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="4">
+        <f>IAS29_test!R33</f>
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="E33" s="4">
+        <f t="shared" si="2"/>
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="F33" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E33),0)</f>
+        <v>1.0041322314049586</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" t="s">
+        <v>212</v>
+      </c>
+      <c r="D34" s="4">
+        <f>IAS29_test!R34</f>
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="2"/>
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="F34" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E34),0)</f>
+        <v>0.97311212814645309</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="4">
+        <f>IAS29_test!R35</f>
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" si="2"/>
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="F35" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E35),0)</f>
+        <v>1.0018651222145871</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="4">
+        <f>IAS29_test!R36</f>
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="2"/>
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="F36" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E36),0)</f>
+        <v>0.99010477299185096</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" t="s">
+        <v>218</v>
+      </c>
+      <c r="D37" s="4">
+        <f>IAS29_test!R37</f>
+        <v>1.67E-2</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" si="2"/>
+        <v>1.67E-2</v>
+      </c>
+      <c r="F37" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E37),0)</f>
+        <v>1.0038359398052523</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="4">
+        <f>IAS29_test!R38</f>
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="2"/>
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="F38" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E38),0)</f>
+        <v>0.99299474605954452</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="4">
+        <f>IAS29_test!R39</f>
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="E39" s="4">
+        <f>(Regional_agg!S25*IAS29_test!R25+Regional_agg!S26*IAS29_test!R26+Regional_agg!S27*IAS29_test!R27+Regional_agg!S39*IAS29_test!R39+Regional_agg!S40*IAS29_test!R40+Regional_agg!S41*IAS29_test!R41+Regional_agg!S42*IAS29_test!R42)/(Regional_agg!S25+Regional_agg!S26+Regional_agg!S27+Regional_agg!S39+Regional_agg!S40+Regional_agg!S41+Regional_agg!S42)</f>
+        <v>1.8992714458767924E-2</v>
+      </c>
+      <c r="F39" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E39),0)</f>
+        <v>1.0015773278046309</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>204</v>
+      </c>
+      <c r="D40" s="4">
+        <f>IAS29_test!R40</f>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="E40" s="4">
+        <f>(Regional_agg!S25*IAS29_test!R25+Regional_agg!S26*IAS29_test!R26+Regional_agg!S27*IAS29_test!R27+Regional_agg!S39*IAS29_test!R39+Regional_agg!S40*IAS29_test!R40+Regional_agg!S41*IAS29_test!R41+Regional_agg!S42*IAS29_test!R42)/(Regional_agg!S25+Regional_agg!S26+Regional_agg!S27+Regional_agg!S39+Regional_agg!S40+Regional_agg!S41+Regional_agg!S42)</f>
+        <v>1.8992714458767924E-2</v>
+      </c>
+      <c r="F40" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E40),0)</f>
+        <v>1.0015773278046309</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>204</v>
+      </c>
+      <c r="D41" s="4">
+        <f>IAS29_test!R41</f>
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="E41" s="4">
+        <f>(Regional_agg!S25*IAS29_test!R25+Regional_agg!S26*IAS29_test!R26+Regional_agg!S27*IAS29_test!R27+Regional_agg!S39*IAS29_test!R39+Regional_agg!S40*IAS29_test!R40+Regional_agg!S41*IAS29_test!R41+Regional_agg!S42*IAS29_test!R42)/(Regional_agg!S25+Regional_agg!S26+Regional_agg!S27+Regional_agg!S39+Regional_agg!S40+Regional_agg!S41+Regional_agg!S42)</f>
+        <v>1.8992714458767924E-2</v>
+      </c>
+      <c r="F41" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E41),0)</f>
+        <v>1.0015773278046309</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="4">
+        <f>IAS29_test!R42</f>
+        <v>1.83E-2</v>
+      </c>
+      <c r="E42" s="4">
+        <f>(Regional_agg!S25*IAS29_test!R25+Regional_agg!S26*IAS29_test!R26+Regional_agg!S27*IAS29_test!R27+Regional_agg!S39*IAS29_test!R39+Regional_agg!S40*IAS29_test!R40+Regional_agg!S41*IAS29_test!R41+Regional_agg!S42*IAS29_test!R42)/(Regional_agg!S25+Regional_agg!S26+Regional_agg!S27+Regional_agg!S39+Regional_agg!S40+Regional_agg!S41+Regional_agg!S42)</f>
+        <v>1.8992714458767924E-2</v>
+      </c>
+      <c r="F42" s="15">
+        <f>IFERROR((1+IAS29_test!R4)/(1+E42),0)</f>
+        <v>1.0015773278046309</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="10">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="15">
+        <f>(Regional_agg!S49*(1+N(Data!J65))*F6+Regional_agg!S50*(1+N(Data!J81))*F7+Regional_agg!S51*(1+N(Data!J97))*F8+Regional_agg!S52*(1+N(Data!J113))*F9+Regional_agg!S53*(1+N(Data!J129))*F10+Regional_agg!S54*(1+N(Data!J145))*F11+Regional_agg!S55*(1+N(Data!J161))*F12+Regional_agg!S56*(1+N(Data!J177))*F13+Regional_agg!S57*(1+N(Data!J193))*F14+Regional_agg!S58*(1+N(Data!J209))*F15+Regional_agg!S59*(1+N(Data!J225))*F16+Regional_agg!S60*(1+N(Data!J241))*F17+Regional_agg!S61*(1+N(Data!J257))*F18+Regional_agg!S62*(1+N(Data!J273))*F19+Regional_agg!S63*(1+N(Data!J289))*F20)/(Regional_agg!S49*(1+N(Data!J65))+Regional_agg!S50*(1+N(Data!J81))+Regional_agg!S51*(1+N(Data!J97))+Regional_agg!S52*(1+N(Data!J113))+Regional_agg!S53*(1+N(Data!J129))+Regional_agg!S54*(1+N(Data!J145))+Regional_agg!S55*(1+N(Data!J161))+Regional_agg!S56*(1+N(Data!J177))+Regional_agg!S57*(1+N(Data!J193))+Regional_agg!S58*(1+N(Data!J209))+Regional_agg!S59*(1+N(Data!J225))+Regional_agg!S60*(1+N(Data!J241))+Regional_agg!S61*(1+N(Data!J257))+Regional_agg!S62*(1+N(Data!J273))+Regional_agg!S63*(1+N(Data!J289)))</f>
+        <v>0.98511538290107492</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="15">
+        <f>(Regional_agg!S64*(1+N(Data!J305))*F21+Regional_agg!S65*(1+N(Data!J321))*F22+Regional_agg!S66*(1+N(Data!J337))*F23+Regional_agg!S67*(1+N(Data!J353))*F24+Regional_agg!S68*(1+N(Data!J369))*F25+Regional_agg!S69*(1+N(Data!J385))*F26+Regional_agg!S70*(1+N(Data!J401))*F27+Regional_agg!S71*(1+N(Data!J417))*F28+Regional_agg!S72*(1+N(Data!J433))*F29+Regional_agg!S73*(1+N(Data!J449))*F30+Regional_agg!S74*(1+N(Data!J465))*F31+Regional_agg!S75*(1+N(Data!J481))*F32+Regional_agg!S76*(1+N(Data!J497))*F33+Regional_agg!S77*(1+N(Data!J513))*F34+Regional_agg!S78*(1+N(Data!J529))*F35+Regional_agg!S79*(1+N(Data!J545))*F36+Regional_agg!S80*(1+N(Data!J561))*F37+Regional_agg!S81*(1+N(Data!J577))*F38+Regional_agg!S82*(1+N(Data!J593))*F39+Regional_agg!S83*(1+N(Data!J609))*F40+Regional_agg!S84*(1+N(Data!J625))*F41+Regional_agg!S85*(1+N(Data!J641))*F42)/(Regional_agg!S64*(1+N(Data!J305))+Regional_agg!S65*(1+N(Data!J321))+Regional_agg!S66*(1+N(Data!J337))+Regional_agg!S67*(1+N(Data!J353))+Regional_agg!S68*(1+N(Data!J369))+Regional_agg!S69*(1+N(Data!J385))+Regional_agg!S70*(1+N(Data!J401))+Regional_agg!S71*(1+N(Data!J417))+Regional_agg!S72*(1+N(Data!J433))+Regional_agg!S73*(1+N(Data!J449))+Regional_agg!S74*(1+N(Data!J465))+Regional_agg!S75*(1+N(Data!J481))+Regional_agg!S76*(1+N(Data!J497))+Regional_agg!S77*(1+N(Data!J513))+Regional_agg!S78*(1+N(Data!J529))+Regional_agg!S79*(1+N(Data!J545))+Regional_agg!S80*(1+N(Data!J561))+Regional_agg!S81*(1+N(Data!J577))+Regional_agg!S82*(1+N(Data!J593))+Regional_agg!S83*(1+N(Data!J609))+Regional_agg!S84*(1+N(Data!J625))+Regional_agg!S85*(1+N(Data!J641)))</f>
+        <v>0.99425917407293729</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>439</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K641"/>
@@ -4973,7 +6000,7 @@
         <v>27</v>
       </c>
       <c r="J3" s="4">
-        <f>IF(D2=0,"",D3/D2-1)</f>
+        <f t="shared" ref="J3:J17" si="0">IF(D2=0,"",D3/D2-1)</f>
         <v>7.9578295050968251E-2</v>
       </c>
       <c r="K3" t="s">
@@ -5009,7 +6036,7 @@
         <v>28</v>
       </c>
       <c r="J4" s="4">
-        <f t="shared" ref="J3:J17" si="0">IF(D3=0,"",D4/D3-1)</f>
+        <f t="shared" si="0"/>
         <v>8.5622524241538045E-2</v>
       </c>
       <c r="K4" t="s">
@@ -33079,59 +34106,59 @@
         <v>33</v>
       </c>
       <c r="E46" s="11">
-        <f>IF(COUNT(C3:E3)&lt;3,"",(1+C3)*(1+D3)*(1+E3)-1)</f>
+        <f t="shared" ref="E46:E85" si="0">IF(COUNT(C3:E3)&lt;3,"",(1+C3)*(1+D3)*(1+E3)-1)</f>
         <v>0.11995952921599984</v>
       </c>
       <c r="F46" s="11">
-        <f t="shared" ref="F46:F85" si="0">IF(COUNT(D3:F3)&lt;3,"",(1+D3)*(1+E3)*(1+F3)-1)</f>
+        <f t="shared" ref="F46:F85" si="1">IF(COUNT(D3:F3)&lt;3,"",(1+D3)*(1+E3)*(1+F3)-1)</f>
         <v>0.14372814071999995</v>
       </c>
       <c r="G46" s="11">
-        <f t="shared" ref="G46:G85" si="1">IF(COUNT(E3:G3)&lt;3,"",(1+E3)*(1+F3)*(1+G3)-1)</f>
+        <f t="shared" ref="G46:G85" si="2">IF(COUNT(E3:G3)&lt;3,"",(1+E3)*(1+F3)*(1+G3)-1)</f>
         <v>0.1528494894400001</v>
       </c>
       <c r="H46" s="11">
-        <f t="shared" ref="H46:H85" si="2">IF(COUNT(F3:H3)&lt;3,"",(1+F3)*(1+G3)*(1+H3)-1)</f>
+        <f t="shared" ref="H46:H85" si="3">IF(COUNT(F3:H3)&lt;3,"",(1+F3)*(1+G3)*(1+H3)-1)</f>
         <v>0.12414784239999999</v>
       </c>
       <c r="I46" s="11">
-        <f t="shared" ref="I46:I85" si="3">IF(COUNT(G3:I3)&lt;3,"",(1+G3)*(1+H3)*(1+I3)-1)</f>
+        <f t="shared" ref="I46:I85" si="4">IF(COUNT(G3:I3)&lt;3,"",(1+G3)*(1+H3)*(1+I3)-1)</f>
         <v>0.13261377943999997</v>
       </c>
       <c r="J46" s="11">
-        <f t="shared" ref="J46:J85" si="4">IF(COUNT(H3:J3)&lt;3,"",(1+H3)*(1+I3)*(1+J3)-1)</f>
+        <f t="shared" ref="J46:J85" si="5">IF(COUNT(H3:J3)&lt;3,"",(1+H3)*(1+I3)*(1+J3)-1)</f>
         <v>0.17916853339999994</v>
       </c>
       <c r="K46" s="11">
-        <f t="shared" ref="K46:K85" si="5">IF(COUNT(I3:K3)&lt;3,"",(1+I3)*(1+J3)*(1+K3)-1)</f>
+        <f t="shared" ref="K46:K85" si="6">IF(COUNT(I3:K3)&lt;3,"",(1+I3)*(1+J3)*(1+K3)-1)</f>
         <v>0.20345894902999984</v>
       </c>
       <c r="L46" s="11">
-        <f t="shared" ref="L46:L85" si="6">IF(COUNT(J3:L3)&lt;3,"",(1+J3)*(1+K3)*(1+L3)-1)</f>
+        <f t="shared" ref="L46:L85" si="7">IF(COUNT(J3:L3)&lt;3,"",(1+J3)*(1+K3)*(1+L3)-1)</f>
         <v>0.1924138626399996</v>
       </c>
       <c r="M46" s="11">
-        <f t="shared" ref="M46:M85" si="7">IF(COUNT(K3:M3)&lt;3,"",(1+K3)*(1+L3)*(1+M3)-1)</f>
+        <f t="shared" ref="M46:M85" si="8">IF(COUNT(K3:M3)&lt;3,"",(1+K3)*(1+L3)*(1+M3)-1)</f>
         <v>0.14721485709599968</v>
       </c>
       <c r="N46" s="11">
-        <f t="shared" ref="N46:N85" si="8">IF(COUNT(L3:N3)&lt;3,"",(1+L3)*(1+M3)*(1+N3)-1)</f>
+        <f t="shared" ref="N46:N85" si="9">IF(COUNT(L3:N3)&lt;3,"",(1+L3)*(1+M3)*(1+N3)-1)</f>
         <v>0.12797321683200003</v>
       </c>
       <c r="O46" s="11">
-        <f t="shared" ref="O46:O85" si="9">IF(COUNT(M3:O3)&lt;3,"",(1+M3)*(1+N3)*(1+O3)-1)</f>
+        <f t="shared" ref="O46:O85" si="10">IF(COUNT(M3:O3)&lt;3,"",(1+M3)*(1+N3)*(1+O3)-1)</f>
         <v>0.11914072984000001</v>
       </c>
       <c r="P46" s="11">
-        <f t="shared" ref="P46:P85" si="10">IF(COUNT(N3:P3)&lt;3,"",(1+N3)*(1+O3)*(1+P3)-1)</f>
+        <f t="shared" ref="P46:P85" si="11">IF(COUNT(N3:P3)&lt;3,"",(1+N3)*(1+O3)*(1+P3)-1)</f>
         <v>0.11817047007999992</v>
       </c>
       <c r="Q46" s="11">
-        <f t="shared" ref="Q46:Q85" si="11">IF(COUNT(O3:Q3)&lt;3,"",(1+O3)*(1+P3)*(1+Q3)-1)</f>
+        <f t="shared" ref="Q46:Q85" si="12">IF(COUNT(O3:Q3)&lt;3,"",(1+O3)*(1+P3)*(1+Q3)-1)</f>
         <v>0.11224339067999978</v>
       </c>
       <c r="R46" s="11">
-        <f t="shared" ref="R46:R85" si="12">IF(COUNT(P3:R3)&lt;3,"",(1+P3)*(1+Q3)*(1+R3)-1)</f>
+        <f t="shared" ref="R46:R85" si="13">IF(COUNT(P3:R3)&lt;3,"",(1+P3)*(1+Q3)*(1+R3)-1)</f>
         <v>9.7791720060000031E-2</v>
       </c>
     </row>
@@ -33143,59 +34170,59 @@
         <v>43</v>
       </c>
       <c r="E47" s="11">
-        <f t="shared" ref="E46:E85" si="13">IF(COUNT(C4:E4)&lt;3,"",(1+C4)*(1+D4)*(1+E4)-1)</f>
+        <f t="shared" si="0"/>
         <v>3.5409382056000194E-2</v>
       </c>
       <c r="F47" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.9402088472000125E-2</v>
       </c>
       <c r="G47" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.5156296932000091E-2</v>
       </c>
       <c r="H47" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5769822171999994E-2</v>
       </c>
       <c r="I47" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.9061893609999823E-2</v>
       </c>
       <c r="J47" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.14466834799999995</v>
       </c>
       <c r="K47" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.17734731199999998</v>
       </c>
       <c r="L47" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.15766863200000003</v>
       </c>
       <c r="M47" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.10096430733999995</v>
       </c>
       <c r="N47" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.2928071520000044E-2</v>
       </c>
       <c r="O47" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.7301535551999931E-2</v>
       </c>
       <c r="P47" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.0632272896000057E-2</v>
       </c>
       <c r="Q47" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.6413427199999875E-2</v>
       </c>
       <c r="R47" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.2665049599999856E-2</v>
       </c>
     </row>
@@ -33207,59 +34234,59 @@
         <v>43</v>
       </c>
       <c r="E48" s="11">
+        <f t="shared" si="0"/>
+        <v>4.2173775440000227E-2</v>
+      </c>
+      <c r="F48" s="11">
+        <f t="shared" si="1"/>
+        <v>5.3921803759999776E-2</v>
+      </c>
+      <c r="G48" s="11">
+        <f t="shared" si="2"/>
+        <v>5.932493240000003E-2</v>
+      </c>
+      <c r="H48" s="11">
+        <f t="shared" si="3"/>
+        <v>5.0149677080000288E-2</v>
+      </c>
+      <c r="I48" s="11">
+        <f t="shared" si="4"/>
+        <v>6.1752973600000205E-2</v>
+      </c>
+      <c r="J48" s="11">
+        <f t="shared" si="5"/>
+        <v>0.11226304640000007</v>
+      </c>
+      <c r="K48" s="11">
+        <f t="shared" si="6"/>
+        <v>0.14715930560000023</v>
+      </c>
+      <c r="L48" s="11">
+        <f t="shared" si="7"/>
+        <v>0.13584303392000008</v>
+      </c>
+      <c r="M48" s="11">
+        <f t="shared" si="8"/>
+        <v>8.5538375207999895E-2</v>
+      </c>
+      <c r="N48" s="11">
+        <f t="shared" si="9"/>
+        <v>7.4043455947999881E-2</v>
+      </c>
+      <c r="O48" s="11">
+        <f t="shared" si="10"/>
+        <v>7.8344665334000085E-2</v>
+      </c>
+      <c r="P48" s="11">
+        <f t="shared" si="11"/>
+        <v>7.8239017772000041E-2</v>
+      </c>
+      <c r="Q48" s="11">
+        <f t="shared" si="12"/>
+        <v>6.8167900268000015E-2</v>
+      </c>
+      <c r="R48" s="11">
         <f t="shared" si="13"/>
-        <v>4.2173775440000227E-2</v>
-      </c>
-      <c r="F48" s="11">
-        <f t="shared" si="0"/>
-        <v>5.3921803759999776E-2</v>
-      </c>
-      <c r="G48" s="11">
-        <f t="shared" si="1"/>
-        <v>5.932493240000003E-2</v>
-      </c>
-      <c r="H48" s="11">
-        <f t="shared" si="2"/>
-        <v>5.0149677080000288E-2</v>
-      </c>
-      <c r="I48" s="11">
-        <f t="shared" si="3"/>
-        <v>6.1752973600000205E-2</v>
-      </c>
-      <c r="J48" s="11">
-        <f t="shared" si="4"/>
-        <v>0.11226304640000007</v>
-      </c>
-      <c r="K48" s="11">
-        <f t="shared" si="5"/>
-        <v>0.14715930560000023</v>
-      </c>
-      <c r="L48" s="11">
-        <f t="shared" si="6"/>
-        <v>0.13584303392000008</v>
-      </c>
-      <c r="M48" s="11">
-        <f t="shared" si="7"/>
-        <v>8.5538375207999895E-2</v>
-      </c>
-      <c r="N48" s="11">
-        <f t="shared" si="8"/>
-        <v>7.4043455947999881E-2</v>
-      </c>
-      <c r="O48" s="11">
-        <f t="shared" si="9"/>
-        <v>7.8344665334000085E-2</v>
-      </c>
-      <c r="P48" s="11">
-        <f t="shared" si="10"/>
-        <v>7.8239017772000041E-2</v>
-      </c>
-      <c r="Q48" s="11">
-        <f t="shared" si="11"/>
-        <v>6.8167900268000015E-2</v>
-      </c>
-      <c r="R48" s="11">
-        <f t="shared" si="12"/>
         <v>5.8503573511999862E-2</v>
       </c>
     </row>
@@ -33271,59 +34298,59 @@
         <v>50</v>
       </c>
       <c r="E49" s="11">
+        <f t="shared" si="0"/>
+        <v>1.004708911616</v>
+      </c>
+      <c r="F49" s="11">
+        <f t="shared" si="1"/>
+        <v>1.3134437319680003</v>
+      </c>
+      <c r="G49" s="11">
+        <f t="shared" si="2"/>
+        <v>1.5831099843200001</v>
+      </c>
+      <c r="H49" s="11">
+        <f t="shared" si="3"/>
+        <v>1.9282669218799997</v>
+      </c>
+      <c r="I49" s="11">
+        <f t="shared" si="4"/>
+        <v>2.2364022481099997</v>
+      </c>
+      <c r="J49" s="11">
+        <f t="shared" si="5"/>
+        <v>2.6343395613259992</v>
+      </c>
+      <c r="K49" s="11">
+        <f t="shared" si="6"/>
+        <v>4.9750876226870009</v>
+      </c>
+      <c r="L49" s="11">
+        <f t="shared" si="7"/>
+        <v>11.878586542315999</v>
+      </c>
+      <c r="M49" s="11">
+        <f t="shared" si="8"/>
+        <v>9.5998318279040014</v>
+      </c>
+      <c r="N49" s="11">
+        <f t="shared" si="9"/>
+        <v>5.0242309459199994</v>
+      </c>
+      <c r="O49" s="11">
+        <f t="shared" si="10"/>
+        <v>1.2183136273599997</v>
+      </c>
+      <c r="P49" s="11">
+        <f t="shared" si="11"/>
+        <v>0.69280838389999988</v>
+      </c>
+      <c r="Q49" s="11">
+        <f t="shared" si="12"/>
+        <v>0.36075260218999983</v>
+      </c>
+      <c r="R49" s="11">
         <f t="shared" si="13"/>
-        <v>1.004708911616</v>
-      </c>
-      <c r="F49" s="11">
-        <f t="shared" si="0"/>
-        <v>1.3134437319680003</v>
-      </c>
-      <c r="G49" s="11">
-        <f t="shared" si="1"/>
-        <v>1.5831099843200001</v>
-      </c>
-      <c r="H49" s="11">
-        <f t="shared" si="2"/>
-        <v>1.9282669218799997</v>
-      </c>
-      <c r="I49" s="11">
-        <f t="shared" si="3"/>
-        <v>2.2364022481099997</v>
-      </c>
-      <c r="J49" s="11">
-        <f t="shared" si="4"/>
-        <v>2.6343395613259992</v>
-      </c>
-      <c r="K49" s="11">
-        <f t="shared" si="5"/>
-        <v>4.9750876226870009</v>
-      </c>
-      <c r="L49" s="11">
-        <f t="shared" si="6"/>
-        <v>11.878586542315999</v>
-      </c>
-      <c r="M49" s="11">
-        <f t="shared" si="7"/>
-        <v>9.5998318279040014</v>
-      </c>
-      <c r="N49" s="11">
-        <f t="shared" si="8"/>
-        <v>5.0242309459199994</v>
-      </c>
-      <c r="O49" s="11">
-        <f t="shared" si="9"/>
-        <v>1.2183136273599997</v>
-      </c>
-      <c r="P49" s="11">
-        <f t="shared" si="10"/>
-        <v>0.69280838389999988</v>
-      </c>
-      <c r="Q49" s="11">
-        <f t="shared" si="11"/>
-        <v>0.36075260218999983</v>
-      </c>
-      <c r="R49" s="11">
-        <f t="shared" si="12"/>
         <v>0.23714233948999985</v>
       </c>
     </row>
@@ -33335,59 +34362,59 @@
         <v>50</v>
       </c>
       <c r="E50" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="0"/>
         <v>0.22649515159</v>
       </c>
       <c r="F50" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.16608719997999977</v>
       </c>
       <c r="G50" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11236182871000011</v>
       </c>
       <c r="H50" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10978119227800009</v>
       </c>
       <c r="I50" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.15945690839000015</v>
       </c>
       <c r="J50" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.22149282703999984</v>
       </c>
       <c r="K50" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.23782516015999988</v>
       </c>
       <c r="L50" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.19290685102400018</v>
       </c>
       <c r="M50" s="11">
-        <f t="shared" si="7"/>
-        <v>0.14640444266600028</v>
-      </c>
-      <c r="N50" s="11">
         <f t="shared" si="8"/>
         <v>0.14640444266600028</v>
       </c>
+      <c r="N50" s="11">
+        <f t="shared" si="9"/>
+        <v>0.14640444266600028</v>
+      </c>
       <c r="O50" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.15189646356600006</v>
       </c>
       <c r="P50" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.13533425008299993</v>
       </c>
       <c r="Q50" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.12480480919399972</v>
       </c>
       <c r="R50" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.10700013690199972</v>
       </c>
     </row>
@@ -33399,59 +34426,59 @@
         <v>50</v>
       </c>
       <c r="E51" s="11">
+        <f t="shared" si="0"/>
+        <v>0.1065524857400002</v>
+      </c>
+      <c r="F51" s="11">
+        <f t="shared" si="1"/>
+        <v>8.6298386576000086E-2</v>
+      </c>
+      <c r="G51" s="11">
+        <f t="shared" si="2"/>
+        <v>7.3528257152000176E-2</v>
+      </c>
+      <c r="H51" s="11">
+        <f t="shared" si="3"/>
+        <v>8.2668691520000115E-2</v>
+      </c>
+      <c r="I51" s="11">
+        <f t="shared" si="4"/>
+        <v>0.10465181215999997</v>
+      </c>
+      <c r="J51" s="11">
+        <f t="shared" si="5"/>
+        <v>0.20245054903999993</v>
+      </c>
+      <c r="K51" s="11">
+        <f t="shared" si="6"/>
+        <v>0.25530936502400015</v>
+      </c>
+      <c r="L51" s="11">
+        <f t="shared" si="7"/>
+        <v>0.25230680722400001</v>
+      </c>
+      <c r="M51" s="11">
+        <f t="shared" si="8"/>
+        <v>0.16896177338600005</v>
+      </c>
+      <c r="N51" s="11">
+        <f t="shared" si="9"/>
+        <v>0.12734508262499999</v>
+      </c>
+      <c r="O51" s="11">
+        <f t="shared" si="10"/>
+        <v>0.1207498922500001</v>
+      </c>
+      <c r="P51" s="11">
+        <f t="shared" si="11"/>
+        <v>0.10655365524999993</v>
+      </c>
+      <c r="Q51" s="11">
+        <f t="shared" si="12"/>
+        <v>9.5461454753999808E-2</v>
+      </c>
+      <c r="R51" s="11">
         <f t="shared" si="13"/>
-        <v>0.1065524857400002</v>
-      </c>
-      <c r="F51" s="11">
-        <f t="shared" si="0"/>
-        <v>8.6298386576000086E-2</v>
-      </c>
-      <c r="G51" s="11">
-        <f t="shared" si="1"/>
-        <v>7.3528257152000176E-2</v>
-      </c>
-      <c r="H51" s="11">
-        <f t="shared" si="2"/>
-        <v>8.2668691520000115E-2</v>
-      </c>
-      <c r="I51" s="11">
-        <f t="shared" si="3"/>
-        <v>0.10465181215999997</v>
-      </c>
-      <c r="J51" s="11">
-        <f t="shared" si="4"/>
-        <v>0.20245054903999993</v>
-      </c>
-      <c r="K51" s="11">
-        <f t="shared" si="5"/>
-        <v>0.25530936502400015</v>
-      </c>
-      <c r="L51" s="11">
-        <f t="shared" si="6"/>
-        <v>0.25230680722400001</v>
-      </c>
-      <c r="M51" s="11">
-        <f t="shared" si="7"/>
-        <v>0.16896177338600005</v>
-      </c>
-      <c r="N51" s="11">
-        <f t="shared" si="8"/>
-        <v>0.12734508262499999</v>
-      </c>
-      <c r="O51" s="11">
-        <f t="shared" si="9"/>
-        <v>0.1207498922500001</v>
-      </c>
-      <c r="P51" s="11">
-        <f t="shared" si="10"/>
-        <v>0.10655365524999993</v>
-      </c>
-      <c r="Q51" s="11">
-        <f t="shared" si="11"/>
-        <v>9.5461454753999808E-2</v>
-      </c>
-      <c r="R51" s="11">
-        <f t="shared" si="12"/>
         <v>8.9437790570999764E-2</v>
       </c>
     </row>
@@ -33463,59 +34490,59 @@
         <v>50</v>
       </c>
       <c r="E52" s="11">
+        <f t="shared" si="0"/>
+        <v>0.177509381568</v>
+      </c>
+      <c r="F52" s="11">
+        <f t="shared" si="1"/>
+        <v>0.15788235596799982</v>
+      </c>
+      <c r="G52" s="11">
+        <f t="shared" si="2"/>
+        <v>0.11491006873599985</v>
+      </c>
+      <c r="H52" s="11">
+        <f t="shared" si="3"/>
+        <v>9.5779614143999936E-2</v>
+      </c>
+      <c r="I52" s="11">
+        <f t="shared" si="4"/>
+        <v>9.8539229599999834E-2</v>
+      </c>
+      <c r="J52" s="11">
+        <f t="shared" si="5"/>
+        <v>0.16921418390000009</v>
+      </c>
+      <c r="K52" s="11">
+        <f t="shared" si="6"/>
+        <v>0.27424161619999965</v>
+      </c>
+      <c r="L52" s="11">
+        <f t="shared" si="7"/>
+        <v>0.31253042225199978</v>
+      </c>
+      <c r="M52" s="11">
+        <f t="shared" si="8"/>
+        <v>0.25249091119599987</v>
+      </c>
+      <c r="N52" s="11">
+        <f t="shared" si="9"/>
+        <v>0.18815139240000001</v>
+      </c>
+      <c r="O52" s="11">
+        <f t="shared" si="10"/>
+        <v>0.18191028200000003</v>
+      </c>
+      <c r="P52" s="11">
+        <f t="shared" si="11"/>
+        <v>0.16707176600000007</v>
+      </c>
+      <c r="Q52" s="11">
+        <f t="shared" si="12"/>
+        <v>0.13888588184000006</v>
+      </c>
+      <c r="R52" s="11">
         <f t="shared" si="13"/>
-        <v>0.177509381568</v>
-      </c>
-      <c r="F52" s="11">
-        <f t="shared" si="0"/>
-        <v>0.15788235596799982</v>
-      </c>
-      <c r="G52" s="11">
-        <f t="shared" si="1"/>
-        <v>0.11491006873599985</v>
-      </c>
-      <c r="H52" s="11">
-        <f t="shared" si="2"/>
-        <v>9.5779614143999936E-2</v>
-      </c>
-      <c r="I52" s="11">
-        <f t="shared" si="3"/>
-        <v>9.8539229599999834E-2</v>
-      </c>
-      <c r="J52" s="11">
-        <f t="shared" si="4"/>
-        <v>0.16921418390000009</v>
-      </c>
-      <c r="K52" s="11">
-        <f t="shared" si="5"/>
-        <v>0.27424161619999965</v>
-      </c>
-      <c r="L52" s="11">
-        <f t="shared" si="6"/>
-        <v>0.31253042225199978</v>
-      </c>
-      <c r="M52" s="11">
-        <f t="shared" si="7"/>
-        <v>0.25249091119599987</v>
-      </c>
-      <c r="N52" s="11">
-        <f t="shared" si="8"/>
-        <v>0.18815139240000001</v>
-      </c>
-      <c r="O52" s="11">
-        <f t="shared" si="9"/>
-        <v>0.18191028200000003</v>
-      </c>
-      <c r="P52" s="11">
-        <f t="shared" si="10"/>
-        <v>0.16707176600000007</v>
-      </c>
-      <c r="Q52" s="11">
-        <f t="shared" si="11"/>
-        <v>0.13888588184000006</v>
-      </c>
-      <c r="R52" s="11">
-        <f t="shared" si="12"/>
         <v>0.10935324463999985</v>
       </c>
     </row>
@@ -33527,59 +34554,59 @@
         <v>50</v>
       </c>
       <c r="E53" s="11">
+        <f t="shared" si="0"/>
+        <v>2.4225513920000052E-2</v>
+      </c>
+      <c r="F53" s="11">
+        <f t="shared" si="1"/>
+        <v>3.8654087628000156E-2</v>
+      </c>
+      <c r="G53" s="11">
+        <f t="shared" si="2"/>
+        <v>6.0677959059999731E-2</v>
+      </c>
+      <c r="H53" s="11">
+        <f t="shared" si="3"/>
+        <v>5.1180596640000076E-2</v>
+      </c>
+      <c r="I53" s="11">
+        <f t="shared" si="4"/>
+        <v>4.6141675759999945E-2</v>
+      </c>
+      <c r="J53" s="11">
+        <f t="shared" si="5"/>
+        <v>0.10936101111200003</v>
+      </c>
+      <c r="K53" s="11">
+        <f t="shared" si="6"/>
+        <v>0.10726829276300021</v>
+      </c>
+      <c r="L53" s="11">
+        <f t="shared" si="7"/>
+        <v>8.397571292900019E-2</v>
+      </c>
+      <c r="M53" s="11">
+        <f t="shared" si="8"/>
+        <v>4.77445210999905E-4</v>
+      </c>
+      <c r="N53" s="11">
+        <f t="shared" si="9"/>
+        <v>-1.0370266072000089E-2</v>
+      </c>
+      <c r="O53" s="11">
+        <f t="shared" si="10"/>
+        <v>2.7887334847999989E-2</v>
+      </c>
+      <c r="P53" s="11">
+        <f t="shared" si="11"/>
+        <v>4.8665203519999922E-2</v>
+      </c>
+      <c r="Q53" s="11">
+        <f t="shared" si="12"/>
+        <v>7.2603960679999968E-2</v>
+      </c>
+      <c r="R53" s="11">
         <f t="shared" si="13"/>
-        <v>2.4225513920000052E-2</v>
-      </c>
-      <c r="F53" s="11">
-        <f t="shared" si="0"/>
-        <v>3.8654087628000156E-2</v>
-      </c>
-      <c r="G53" s="11">
-        <f t="shared" si="1"/>
-        <v>6.0677959059999731E-2</v>
-      </c>
-      <c r="H53" s="11">
-        <f t="shared" si="2"/>
-        <v>5.1180596640000076E-2</v>
-      </c>
-      <c r="I53" s="11">
-        <f t="shared" si="3"/>
-        <v>4.6141675759999945E-2</v>
-      </c>
-      <c r="J53" s="11">
-        <f t="shared" si="4"/>
-        <v>0.10936101111200003</v>
-      </c>
-      <c r="K53" s="11">
-        <f t="shared" si="5"/>
-        <v>0.10726829276300021</v>
-      </c>
-      <c r="L53" s="11">
-        <f t="shared" si="6"/>
-        <v>8.397571292900019E-2</v>
-      </c>
-      <c r="M53" s="11">
-        <f t="shared" si="7"/>
-        <v>4.77445210999905E-4</v>
-      </c>
-      <c r="N53" s="11">
-        <f t="shared" si="8"/>
-        <v>-1.0370266072000089E-2</v>
-      </c>
-      <c r="O53" s="11">
-        <f t="shared" si="9"/>
-        <v>2.7887334847999989E-2</v>
-      </c>
-      <c r="P53" s="11">
-        <f t="shared" si="10"/>
-        <v>4.8665203519999922E-2</v>
-      </c>
-      <c r="Q53" s="11">
-        <f t="shared" si="11"/>
-        <v>7.2603960679999968E-2</v>
-      </c>
-      <c r="R53" s="11">
-        <f t="shared" si="12"/>
         <v>5.9538599210000154E-2</v>
       </c>
     </row>
@@ -33591,59 +34618,59 @@
         <v>50</v>
       </c>
       <c r="E54" s="11">
+        <f t="shared" si="0"/>
+        <v>6.2129094602000112E-2</v>
+      </c>
+      <c r="F54" s="11">
+        <f t="shared" si="1"/>
+        <v>1.932520014800021E-2</v>
+      </c>
+      <c r="G54" s="11">
+        <f t="shared" si="2"/>
+        <v>4.696135051999839E-3</v>
+      </c>
+      <c r="H54" s="11">
+        <f t="shared" si="3"/>
+        <v>-2.9076198040001167E-3</v>
+      </c>
+      <c r="I54" s="11">
+        <f t="shared" si="4"/>
+        <v>5.8989806599996086E-4</v>
+      </c>
+      <c r="J54" s="11">
+        <f t="shared" si="5"/>
+        <v>3.2522556626000121E-2</v>
+      </c>
+      <c r="K54" s="11">
+        <f t="shared" si="6"/>
+        <v>5.9045311442000203E-2</v>
+      </c>
+      <c r="L54" s="11">
+        <f t="shared" si="7"/>
+        <v>7.4064230270000087E-2</v>
+      </c>
+      <c r="M54" s="11">
+        <f t="shared" si="8"/>
+        <v>4.5414213110000157E-2</v>
+      </c>
+      <c r="N54" s="11">
+        <f t="shared" si="9"/>
+        <v>4.6948278185000136E-2</v>
+      </c>
+      <c r="O54" s="11">
+        <f t="shared" si="10"/>
+        <v>5.8701316463000142E-2</v>
+      </c>
+      <c r="P54" s="11">
+        <f t="shared" si="11"/>
+        <v>7.4154508154000043E-2</v>
+      </c>
+      <c r="Q54" s="11">
+        <f t="shared" si="12"/>
+        <v>7.1216506177999905E-2</v>
+      </c>
+      <c r="R54" s="11">
         <f t="shared" si="13"/>
-        <v>6.2129094602000112E-2</v>
-      </c>
-      <c r="F54" s="11">
-        <f t="shared" si="0"/>
-        <v>1.932520014800021E-2</v>
-      </c>
-      <c r="G54" s="11">
-        <f t="shared" si="1"/>
-        <v>4.696135051999839E-3</v>
-      </c>
-      <c r="H54" s="11">
-        <f t="shared" si="2"/>
-        <v>-2.9076198040001167E-3</v>
-      </c>
-      <c r="I54" s="11">
-        <f t="shared" si="3"/>
-        <v>5.8989806599996086E-4</v>
-      </c>
-      <c r="J54" s="11">
-        <f t="shared" si="4"/>
-        <v>3.2522556626000121E-2</v>
-      </c>
-      <c r="K54" s="11">
-        <f t="shared" si="5"/>
-        <v>5.9045311442000203E-2</v>
-      </c>
-      <c r="L54" s="11">
-        <f t="shared" si="6"/>
-        <v>7.4064230270000087E-2</v>
-      </c>
-      <c r="M54" s="11">
-        <f t="shared" si="7"/>
-        <v>4.5414213110000157E-2</v>
-      </c>
-      <c r="N54" s="11">
-        <f t="shared" si="8"/>
-        <v>4.6948278185000136E-2</v>
-      </c>
-      <c r="O54" s="11">
-        <f t="shared" si="9"/>
-        <v>5.8701316463000142E-2</v>
-      </c>
-      <c r="P54" s="11">
-        <f t="shared" si="10"/>
-        <v>7.4154508154000043E-2</v>
-      </c>
-      <c r="Q54" s="11">
-        <f t="shared" si="11"/>
-        <v>7.1216506177999905E-2</v>
-      </c>
-      <c r="R54" s="11">
-        <f t="shared" si="12"/>
         <v>6.474894133400011E-2</v>
       </c>
     </row>
@@ -33655,59 +34682,59 @@
         <v>50</v>
       </c>
       <c r="E55" s="11">
+        <f t="shared" si="0"/>
+        <v>8.7426276199999986E-3</v>
+      </c>
+      <c r="F55" s="11">
+        <f t="shared" si="1"/>
+        <v>2.7236750539999965E-2</v>
+      </c>
+      <c r="G55" s="11">
+        <f t="shared" si="2"/>
+        <v>2.1824867062999687E-2</v>
+      </c>
+      <c r="H55" s="11">
+        <f t="shared" si="3"/>
+        <v>7.8646817689997928E-3</v>
+      </c>
+      <c r="I55" s="11">
+        <f t="shared" si="4"/>
+        <v>3.1593220126999721E-2</v>
+      </c>
+      <c r="J55" s="11">
+        <f t="shared" si="5"/>
+        <v>0.1050943659200001</v>
+      </c>
+      <c r="K55" s="11">
+        <f t="shared" si="6"/>
+        <v>0.15412093519999992</v>
+      </c>
+      <c r="L55" s="11">
+        <f t="shared" si="7"/>
+        <v>0.12489703599999991</v>
+      </c>
+      <c r="M55" s="11">
+        <f t="shared" si="8"/>
+        <v>5.2072545049999697E-2</v>
+      </c>
+      <c r="N55" s="11">
+        <f t="shared" si="9"/>
+        <v>3.5591254819999918E-2</v>
+      </c>
+      <c r="O55" s="11">
+        <f t="shared" si="10"/>
+        <v>5.3766728503999994E-2</v>
+      </c>
+      <c r="P55" s="11">
+        <f t="shared" si="11"/>
+        <v>7.6889477383999871E-2</v>
+      </c>
+      <c r="Q55" s="11">
+        <f t="shared" si="12"/>
+        <v>7.8361499712000127E-2</v>
+      </c>
+      <c r="R55" s="11">
         <f t="shared" si="13"/>
-        <v>8.7426276199999986E-3</v>
-      </c>
-      <c r="F55" s="11">
-        <f t="shared" si="0"/>
-        <v>2.7236750539999965E-2</v>
-      </c>
-      <c r="G55" s="11">
-        <f t="shared" si="1"/>
-        <v>2.1824867062999687E-2</v>
-      </c>
-      <c r="H55" s="11">
-        <f t="shared" si="2"/>
-        <v>7.8646817689997928E-3</v>
-      </c>
-      <c r="I55" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1593220126999721E-2</v>
-      </c>
-      <c r="J55" s="11">
-        <f t="shared" si="4"/>
-        <v>0.1050943659200001</v>
-      </c>
-      <c r="K55" s="11">
-        <f t="shared" si="5"/>
-        <v>0.15412093519999992</v>
-      </c>
-      <c r="L55" s="11">
-        <f t="shared" si="6"/>
-        <v>0.12489703599999991</v>
-      </c>
-      <c r="M55" s="11">
-        <f t="shared" si="7"/>
-        <v>5.2072545049999697E-2</v>
-      </c>
-      <c r="N55" s="11">
-        <f t="shared" si="8"/>
-        <v>3.5591254819999918E-2</v>
-      </c>
-      <c r="O55" s="11">
-        <f t="shared" si="9"/>
-        <v>5.3766728503999994E-2</v>
-      </c>
-      <c r="P55" s="11">
-        <f t="shared" si="10"/>
-        <v>7.6889477383999871E-2</v>
-      </c>
-      <c r="Q55" s="11">
-        <f t="shared" si="11"/>
-        <v>7.8361499712000127E-2</v>
-      </c>
-      <c r="R55" s="11">
-        <f t="shared" si="12"/>
         <v>7.867674863999996E-2</v>
       </c>
     </row>
@@ -33719,59 +34746,59 @@
         <v>50</v>
       </c>
       <c r="E56" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11673383891000011</v>
+      </c>
+      <c r="F56" s="11">
+        <f t="shared" si="1"/>
+        <v>0.13156690874999999</v>
+      </c>
+      <c r="G56" s="11">
+        <f t="shared" si="2"/>
+        <v>0.12344172750000015</v>
+      </c>
+      <c r="H56" s="11">
+        <f t="shared" si="3"/>
+        <v>0.11042348875000019</v>
+      </c>
+      <c r="I56" s="11">
+        <f t="shared" si="4"/>
+        <v>0.11588195601999995</v>
+      </c>
+      <c r="J56" s="11">
+        <f t="shared" si="5"/>
+        <v>0.15020850799399987</v>
+      </c>
+      <c r="K56" s="11">
+        <f t="shared" si="6"/>
+        <v>0.18364156219399996</v>
+      </c>
+      <c r="L56" s="11">
+        <f t="shared" si="7"/>
+        <v>0.16786118840299991</v>
+      </c>
+      <c r="M56" s="11">
+        <f t="shared" si="8"/>
+        <v>0.10984506986600007</v>
+      </c>
+      <c r="N56" s="11">
+        <f t="shared" si="9"/>
+        <v>7.7347017259999706E-2</v>
+      </c>
+      <c r="O56" s="11">
+        <f t="shared" si="10"/>
+        <v>8.4363858919999979E-2</v>
+      </c>
+      <c r="P56" s="11">
+        <f t="shared" si="11"/>
+        <v>0.10539355770000003</v>
+      </c>
+      <c r="Q56" s="11">
+        <f t="shared" si="12"/>
+        <v>0.10571520471000051</v>
+      </c>
+      <c r="R56" s="11">
         <f t="shared" si="13"/>
-        <v>0.11673383891000011</v>
-      </c>
-      <c r="F56" s="11">
-        <f t="shared" si="0"/>
-        <v>0.13156690874999999</v>
-      </c>
-      <c r="G56" s="11">
-        <f t="shared" si="1"/>
-        <v>0.12344172750000015</v>
-      </c>
-      <c r="H56" s="11">
-        <f t="shared" si="2"/>
-        <v>0.11042348875000019</v>
-      </c>
-      <c r="I56" s="11">
-        <f t="shared" si="3"/>
-        <v>0.11588195601999995</v>
-      </c>
-      <c r="J56" s="11">
-        <f t="shared" si="4"/>
-        <v>0.15020850799399987</v>
-      </c>
-      <c r="K56" s="11">
-        <f t="shared" si="5"/>
-        <v>0.18364156219399996</v>
-      </c>
-      <c r="L56" s="11">
-        <f t="shared" si="6"/>
-        <v>0.16786118840299991</v>
-      </c>
-      <c r="M56" s="11">
-        <f t="shared" si="7"/>
-        <v>0.10984506986600007</v>
-      </c>
-      <c r="N56" s="11">
-        <f t="shared" si="8"/>
-        <v>7.7347017259999706E-2</v>
-      </c>
-      <c r="O56" s="11">
-        <f t="shared" si="9"/>
-        <v>8.4363858919999979E-2</v>
-      </c>
-      <c r="P56" s="11">
-        <f t="shared" si="10"/>
-        <v>0.10539355770000003</v>
-      </c>
-      <c r="Q56" s="11">
-        <f t="shared" si="11"/>
-        <v>0.10571520471000051</v>
-      </c>
-      <c r="R56" s="11">
-        <f t="shared" si="12"/>
         <v>0.10037564896000029</v>
       </c>
     </row>
@@ -33783,59 +34810,59 @@
         <v>50</v>
       </c>
       <c r="E57" s="11">
+        <f t="shared" si="0"/>
+        <v>0.10130413913599967</v>
+      </c>
+      <c r="F57" s="11">
+        <f t="shared" si="1"/>
+        <v>0.11400820975999992</v>
+      </c>
+      <c r="G57" s="11">
+        <f t="shared" si="2"/>
+        <v>0.13190261733499997</v>
+      </c>
+      <c r="H57" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12689275296500013</v>
+      </c>
+      <c r="I57" s="11">
+        <f t="shared" si="4"/>
+        <v>0.12829664427199994</v>
+      </c>
+      <c r="J57" s="11">
+        <f t="shared" si="5"/>
+        <v>0.17932241950399996</v>
+      </c>
+      <c r="K57" s="11">
+        <f t="shared" si="6"/>
+        <v>0.21568115651199982</v>
+      </c>
+      <c r="L57" s="11">
+        <f t="shared" si="7"/>
+        <v>0.21719377663399997</v>
+      </c>
+      <c r="M57" s="11">
+        <f t="shared" si="8"/>
+        <v>0.16709569196000018</v>
+      </c>
+      <c r="N57" s="11">
+        <f t="shared" si="9"/>
+        <v>0.15024469472000002</v>
+      </c>
+      <c r="O57" s="11">
+        <f t="shared" si="10"/>
+        <v>0.14749580672000007</v>
+      </c>
+      <c r="P57" s="11">
+        <f t="shared" si="11"/>
+        <v>0.14288827097600021</v>
+      </c>
+      <c r="Q57" s="11">
+        <f t="shared" si="12"/>
+        <v>0.13005904571200011</v>
+      </c>
+      <c r="R57" s="11">
         <f t="shared" si="13"/>
-        <v>0.10130413913599967</v>
-      </c>
-      <c r="F57" s="11">
-        <f t="shared" si="0"/>
-        <v>0.11400820975999992</v>
-      </c>
-      <c r="G57" s="11">
-        <f t="shared" si="1"/>
-        <v>0.13190261733499997</v>
-      </c>
-      <c r="H57" s="11">
-        <f t="shared" si="2"/>
-        <v>0.12689275296500013</v>
-      </c>
-      <c r="I57" s="11">
-        <f t="shared" si="3"/>
-        <v>0.12829664427199994</v>
-      </c>
-      <c r="J57" s="11">
-        <f t="shared" si="4"/>
-        <v>0.17932241950399996</v>
-      </c>
-      <c r="K57" s="11">
-        <f t="shared" si="5"/>
-        <v>0.21568115651199982</v>
-      </c>
-      <c r="L57" s="11">
-        <f t="shared" si="6"/>
-        <v>0.21719377663399997</v>
-      </c>
-      <c r="M57" s="11">
-        <f t="shared" si="7"/>
-        <v>0.16709569196000018</v>
-      </c>
-      <c r="N57" s="11">
-        <f t="shared" si="8"/>
-        <v>0.15024469472000002</v>
-      </c>
-      <c r="O57" s="11">
-        <f t="shared" si="9"/>
-        <v>0.14749580672000007</v>
-      </c>
-      <c r="P57" s="11">
-        <f t="shared" si="10"/>
-        <v>0.14288827097600021</v>
-      </c>
-      <c r="Q57" s="11">
-        <f t="shared" si="11"/>
-        <v>0.13005904571200011</v>
-      </c>
-      <c r="R57" s="11">
-        <f t="shared" si="12"/>
         <v>0.12247911727200012</v>
       </c>
     </row>
@@ -33847,59 +34874,59 @@
         <v>50</v>
       </c>
       <c r="E58" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11805740800000009</v>
+      </c>
+      <c r="F58" s="11">
+        <f t="shared" si="1"/>
+        <v>0.12827043239999991</v>
+      </c>
+      <c r="G58" s="11">
+        <f t="shared" si="2"/>
+        <v>0.14854267934999998</v>
+      </c>
+      <c r="H58" s="11">
+        <f t="shared" si="3"/>
+        <v>0.14666254208000007</v>
+      </c>
+      <c r="I58" s="11">
+        <f t="shared" si="4"/>
+        <v>0.14644402611199991</v>
+      </c>
+      <c r="J58" s="11">
+        <f t="shared" si="5"/>
+        <v>0.20181886092799983</v>
+      </c>
+      <c r="K58" s="11">
+        <f t="shared" si="6"/>
+        <v>0.25641537746900012</v>
+      </c>
+      <c r="L58" s="11">
+        <f t="shared" si="7"/>
+        <v>0.2528232244790003</v>
+      </c>
+      <c r="M58" s="11">
+        <f t="shared" si="8"/>
+        <v>0.15767352905600007</v>
+      </c>
+      <c r="N58" s="11">
+        <f t="shared" si="9"/>
+        <v>0.10971749855999979</v>
+      </c>
+      <c r="O58" s="11">
+        <f t="shared" si="10"/>
+        <v>9.8262897599999954E-2</v>
+      </c>
+      <c r="P58" s="11">
+        <f t="shared" si="11"/>
+        <v>0.12376136024999984</v>
+      </c>
+      <c r="Q58" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12040846302500019</v>
+      </c>
+      <c r="R58" s="11">
         <f t="shared" si="13"/>
-        <v>0.11805740800000009</v>
-      </c>
-      <c r="F58" s="11">
-        <f t="shared" si="0"/>
-        <v>0.12827043239999991</v>
-      </c>
-      <c r="G58" s="11">
-        <f t="shared" si="1"/>
-        <v>0.14854267934999998</v>
-      </c>
-      <c r="H58" s="11">
-        <f t="shared" si="2"/>
-        <v>0.14666254208000007</v>
-      </c>
-      <c r="I58" s="11">
-        <f t="shared" si="3"/>
-        <v>0.14644402611199991</v>
-      </c>
-      <c r="J58" s="11">
-        <f t="shared" si="4"/>
-        <v>0.20181886092799983</v>
-      </c>
-      <c r="K58" s="11">
-        <f t="shared" si="5"/>
-        <v>0.25641537746900012</v>
-      </c>
-      <c r="L58" s="11">
-        <f t="shared" si="6"/>
-        <v>0.2528232244790003</v>
-      </c>
-      <c r="M58" s="11">
-        <f t="shared" si="7"/>
-        <v>0.15767352905600007</v>
-      </c>
-      <c r="N58" s="11">
-        <f t="shared" si="8"/>
-        <v>0.10971749855999979</v>
-      </c>
-      <c r="O58" s="11">
-        <f t="shared" si="9"/>
-        <v>9.8262897599999954E-2</v>
-      </c>
-      <c r="P58" s="11">
-        <f t="shared" si="10"/>
-        <v>0.12376136024999984</v>
-      </c>
-      <c r="Q58" s="11">
-        <f t="shared" si="11"/>
-        <v>0.12040846302500019</v>
-      </c>
-      <c r="R58" s="11">
-        <f t="shared" si="12"/>
         <v>0.1182444679250001</v>
       </c>
     </row>
@@ -33911,59 +34938,59 @@
         <v>50</v>
       </c>
       <c r="E59" s="11">
+        <f t="shared" si="0"/>
+        <v>1.7687891168000069E-2</v>
+      </c>
+      <c r="F59" s="11">
+        <f t="shared" si="1"/>
+        <v>2.3988734912000043E-2</v>
+      </c>
+      <c r="G59" s="11">
+        <f t="shared" si="2"/>
+        <v>1.2807599232000033E-2</v>
+      </c>
+      <c r="H59" s="11">
+        <f t="shared" si="3"/>
+        <v>-1.1588935919999988E-2</v>
+      </c>
+      <c r="I59" s="11">
+        <f t="shared" si="4"/>
+        <v>-3.0546204599999349E-3</v>
+      </c>
+      <c r="J59" s="11">
+        <f t="shared" si="5"/>
+        <v>2.9163004209999954E-2</v>
+      </c>
+      <c r="K59" s="11">
+        <f t="shared" si="6"/>
+        <v>6.0942136081999942E-2</v>
+      </c>
+      <c r="L59" s="11">
+        <f t="shared" si="7"/>
+        <v>5.1129230365999812E-2</v>
+      </c>
+      <c r="M59" s="11">
+        <f t="shared" si="8"/>
+        <v>1.9756814098999875E-2</v>
+      </c>
+      <c r="N59" s="11">
+        <f t="shared" si="9"/>
+        <v>2.6890791219999821E-2</v>
+      </c>
+      <c r="O59" s="11">
+        <f t="shared" si="10"/>
+        <v>4.4942203479999776E-2</v>
+      </c>
+      <c r="P59" s="11">
+        <f t="shared" si="11"/>
+        <v>6.7769881640000085E-2</v>
+      </c>
+      <c r="Q59" s="11">
+        <f t="shared" si="12"/>
+        <v>6.5262398552000001E-2</v>
+      </c>
+      <c r="R59" s="11">
         <f t="shared" si="13"/>
-        <v>1.7687891168000069E-2</v>
-      </c>
-      <c r="F59" s="11">
-        <f t="shared" si="0"/>
-        <v>2.3988734912000043E-2</v>
-      </c>
-      <c r="G59" s="11">
-        <f t="shared" si="1"/>
-        <v>1.2807599232000033E-2</v>
-      </c>
-      <c r="H59" s="11">
-        <f t="shared" si="2"/>
-        <v>-1.1588935919999988E-2</v>
-      </c>
-      <c r="I59" s="11">
-        <f t="shared" si="3"/>
-        <v>-3.0546204599999349E-3</v>
-      </c>
-      <c r="J59" s="11">
-        <f t="shared" si="4"/>
-        <v>2.9163004209999954E-2</v>
-      </c>
-      <c r="K59" s="11">
-        <f t="shared" si="5"/>
-        <v>6.0942136081999942E-2</v>
-      </c>
-      <c r="L59" s="11">
-        <f t="shared" si="6"/>
-        <v>5.1129230365999812E-2</v>
-      </c>
-      <c r="M59" s="11">
-        <f t="shared" si="7"/>
-        <v>1.9756814098999875E-2</v>
-      </c>
-      <c r="N59" s="11">
-        <f t="shared" si="8"/>
-        <v>2.6890791219999821E-2</v>
-      </c>
-      <c r="O59" s="11">
-        <f t="shared" si="9"/>
-        <v>4.4942203479999776E-2</v>
-      </c>
-      <c r="P59" s="11">
-        <f t="shared" si="10"/>
-        <v>6.7769881640000085E-2</v>
-      </c>
-      <c r="Q59" s="11">
-        <f t="shared" si="11"/>
-        <v>6.5262398552000001E-2</v>
-      </c>
-      <c r="R59" s="11">
-        <f t="shared" si="12"/>
         <v>6.0063967952000086E-2</v>
       </c>
     </row>
@@ -33975,59 +35002,59 @@
         <v>50</v>
       </c>
       <c r="E60" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11212545612000002</v>
+      </c>
+      <c r="F60" s="11">
+        <f t="shared" si="1"/>
+        <v>0.12129162151999995</v>
+      </c>
+      <c r="G60" s="11">
+        <f t="shared" si="2"/>
+        <v>0.10696442528000016</v>
+      </c>
+      <c r="H60" s="11">
+        <f t="shared" si="3"/>
+        <v>8.7410903096000192E-2</v>
+      </c>
+      <c r="I60" s="11">
+        <f t="shared" si="4"/>
+        <v>9.5881790108000242E-2</v>
+      </c>
+      <c r="J60" s="11">
+        <f t="shared" si="5"/>
+        <v>0.17063978299100002</v>
+      </c>
+      <c r="K60" s="11">
+        <f t="shared" si="6"/>
+        <v>0.20353778612899998</v>
+      </c>
+      <c r="L60" s="11">
+        <f t="shared" si="7"/>
+        <v>0.19262681278400007</v>
+      </c>
+      <c r="M60" s="11">
+        <f t="shared" si="8"/>
+        <v>0.13037162796800006</v>
+      </c>
+      <c r="N60" s="11">
+        <f t="shared" si="9"/>
+        <v>0.1028226682879998</v>
+      </c>
+      <c r="O60" s="11">
+        <f t="shared" si="10"/>
+        <v>9.1352632832000014E-2</v>
+      </c>
+      <c r="P60" s="11">
+        <f t="shared" si="11"/>
+        <v>8.3904916864000034E-2</v>
+      </c>
+      <c r="Q60" s="11">
+        <f t="shared" si="12"/>
+        <v>9.6752927732000282E-2</v>
+      </c>
+      <c r="R60" s="11">
         <f t="shared" si="13"/>
-        <v>0.11212545612000002</v>
-      </c>
-      <c r="F60" s="11">
-        <f t="shared" si="0"/>
-        <v>0.12129162151999995</v>
-      </c>
-      <c r="G60" s="11">
-        <f t="shared" si="1"/>
-        <v>0.10696442528000016</v>
-      </c>
-      <c r="H60" s="11">
-        <f t="shared" si="2"/>
-        <v>8.7410903096000192E-2</v>
-      </c>
-      <c r="I60" s="11">
-        <f t="shared" si="3"/>
-        <v>9.5881790108000242E-2</v>
-      </c>
-      <c r="J60" s="11">
-        <f t="shared" si="4"/>
-        <v>0.17063978299100002</v>
-      </c>
-      <c r="K60" s="11">
-        <f t="shared" si="5"/>
-        <v>0.20353778612899998</v>
-      </c>
-      <c r="L60" s="11">
-        <f t="shared" si="6"/>
-        <v>0.19262681278400007</v>
-      </c>
-      <c r="M60" s="11">
-        <f t="shared" si="7"/>
-        <v>0.13037162796800006</v>
-      </c>
-      <c r="N60" s="11">
-        <f t="shared" si="8"/>
-        <v>0.1028226682879998</v>
-      </c>
-      <c r="O60" s="11">
-        <f t="shared" si="9"/>
-        <v>9.1352632832000014E-2</v>
-      </c>
-      <c r="P60" s="11">
-        <f t="shared" si="10"/>
-        <v>8.3904916864000034E-2</v>
-      </c>
-      <c r="Q60" s="11">
-        <f t="shared" si="11"/>
-        <v>9.6752927732000282E-2</v>
-      </c>
-      <c r="R60" s="11">
-        <f t="shared" si="12"/>
         <v>0.10326343070900013</v>
       </c>
     </row>
@@ -34039,59 +35066,59 @@
         <v>50</v>
       </c>
       <c r="E61" s="11">
+        <f t="shared" si="0"/>
+        <v>0.10270933460000009</v>
+      </c>
+      <c r="F61" s="11">
+        <f t="shared" si="1"/>
+        <v>7.8961948640000168E-2</v>
+      </c>
+      <c r="G61" s="11">
+        <f t="shared" si="2"/>
+        <v>6.3859189440000241E-2</v>
+      </c>
+      <c r="H61" s="11">
+        <f t="shared" si="3"/>
+        <v>5.3820829384000346E-2</v>
+      </c>
+      <c r="I61" s="11">
+        <f t="shared" si="4"/>
+        <v>8.1487266476000242E-2</v>
+      </c>
+      <c r="J61" s="11">
+        <f t="shared" si="5"/>
+        <v>0.1422640131920001</v>
+      </c>
+      <c r="K61" s="11">
+        <f t="shared" si="6"/>
+        <v>0.19195692862399993</v>
+      </c>
+      <c r="L61" s="11">
+        <f t="shared" si="7"/>
+        <v>0.17327170267999992</v>
+      </c>
+      <c r="M61" s="11">
+        <f t="shared" si="8"/>
+        <v>0.10388466649999994</v>
+      </c>
+      <c r="N61" s="11">
+        <f t="shared" si="9"/>
+        <v>7.9159976999999992E-2</v>
+      </c>
+      <c r="O61" s="11">
+        <f t="shared" si="10"/>
+        <v>9.0020111599999897E-2</v>
+      </c>
+      <c r="P61" s="11">
+        <f t="shared" si="11"/>
+        <v>9.5497059944000151E-2</v>
+      </c>
+      <c r="Q61" s="11">
+        <f t="shared" si="12"/>
+        <v>7.9256537492000234E-2</v>
+      </c>
+      <c r="R61" s="11">
         <f t="shared" si="13"/>
-        <v>0.10270933460000009</v>
-      </c>
-      <c r="F61" s="11">
-        <f t="shared" si="0"/>
-        <v>7.8961948640000168E-2</v>
-      </c>
-      <c r="G61" s="11">
-        <f t="shared" si="1"/>
-        <v>6.3859189440000241E-2</v>
-      </c>
-      <c r="H61" s="11">
-        <f t="shared" si="2"/>
-        <v>5.3820829384000346E-2</v>
-      </c>
-      <c r="I61" s="11">
-        <f t="shared" si="3"/>
-        <v>8.1487266476000242E-2</v>
-      </c>
-      <c r="J61" s="11">
-        <f t="shared" si="4"/>
-        <v>0.1422640131920001</v>
-      </c>
-      <c r="K61" s="11">
-        <f t="shared" si="5"/>
-        <v>0.19195692862399993</v>
-      </c>
-      <c r="L61" s="11">
-        <f t="shared" si="6"/>
-        <v>0.17327170267999992</v>
-      </c>
-      <c r="M61" s="11">
-        <f t="shared" si="7"/>
-        <v>0.10388466649999994</v>
-      </c>
-      <c r="N61" s="11">
-        <f t="shared" si="8"/>
-        <v>7.9159976999999992E-2</v>
-      </c>
-      <c r="O61" s="11">
-        <f t="shared" si="9"/>
-        <v>9.0020111599999897E-2</v>
-      </c>
-      <c r="P61" s="11">
-        <f t="shared" si="10"/>
-        <v>9.5497059944000151E-2</v>
-      </c>
-      <c r="Q61" s="11">
-        <f t="shared" si="11"/>
-        <v>7.9256537492000234E-2</v>
-      </c>
-      <c r="R61" s="11">
-        <f t="shared" si="12"/>
         <v>7.2888318418000031E-2</v>
       </c>
     </row>
@@ -34103,59 +35130,59 @@
         <v>50</v>
       </c>
       <c r="E62" s="11">
+        <f t="shared" si="0"/>
+        <v>0.265566560136</v>
+      </c>
+      <c r="F62" s="11">
+        <f t="shared" si="1"/>
+        <v>0.25322184168800033</v>
+      </c>
+      <c r="G62" s="11">
+        <f t="shared" si="2"/>
+        <v>0.23310445349600006</v>
+      </c>
+      <c r="H62" s="11">
+        <f t="shared" si="3"/>
+        <v>0.27420019596799983</v>
+      </c>
+      <c r="I62" s="11">
+        <f t="shared" si="4"/>
+        <v>0.2758579231999998</v>
+      </c>
+      <c r="J62" s="11">
+        <f t="shared" si="5"/>
+        <v>0.2902864239999996</v>
+      </c>
+      <c r="K62" s="11">
+        <f t="shared" si="6"/>
+        <v>0.24455743174999967</v>
+      </c>
+      <c r="L62" s="11">
+        <f t="shared" si="7"/>
+        <v>0.21106122244999992</v>
+      </c>
+      <c r="M62" s="11">
+        <f t="shared" si="8"/>
+        <v>0.16166413317499995</v>
+      </c>
+      <c r="N62" s="11">
+        <f t="shared" si="9"/>
+        <v>0.15200828697499991</v>
+      </c>
+      <c r="O62" s="11">
+        <f t="shared" si="10"/>
+        <v>0.16376459471999993</v>
+      </c>
+      <c r="P62" s="11">
+        <f t="shared" si="11"/>
+        <v>0.16498785420800011</v>
+      </c>
+      <c r="Q62" s="11">
+        <f t="shared" si="12"/>
+        <v>0.15355878963200009</v>
+      </c>
+      <c r="R62" s="11">
         <f t="shared" si="13"/>
-        <v>0.265566560136</v>
-      </c>
-      <c r="F62" s="11">
-        <f t="shared" si="0"/>
-        <v>0.25322184168800033</v>
-      </c>
-      <c r="G62" s="11">
-        <f t="shared" si="1"/>
-        <v>0.23310445349600006</v>
-      </c>
-      <c r="H62" s="11">
-        <f t="shared" si="2"/>
-        <v>0.27420019596799983</v>
-      </c>
-      <c r="I62" s="11">
-        <f t="shared" si="3"/>
-        <v>0.2758579231999998</v>
-      </c>
-      <c r="J62" s="11">
-        <f t="shared" si="4"/>
-        <v>0.2902864239999996</v>
-      </c>
-      <c r="K62" s="11">
-        <f t="shared" si="5"/>
-        <v>0.24455743174999967</v>
-      </c>
-      <c r="L62" s="11">
-        <f t="shared" si="6"/>
-        <v>0.21106122244999992</v>
-      </c>
-      <c r="M62" s="11">
-        <f t="shared" si="7"/>
-        <v>0.16166413317499995</v>
-      </c>
-      <c r="N62" s="11">
-        <f t="shared" si="8"/>
-        <v>0.15200828697499991</v>
-      </c>
-      <c r="O62" s="11">
-        <f t="shared" si="9"/>
-        <v>0.16376459471999993</v>
-      </c>
-      <c r="P62" s="11">
-        <f t="shared" si="10"/>
-        <v>0.16498785420800011</v>
-      </c>
-      <c r="Q62" s="11">
-        <f t="shared" si="11"/>
-        <v>0.15355878963200009</v>
-      </c>
-      <c r="R62" s="11">
-        <f t="shared" si="12"/>
         <v>0.12295550225600005</v>
       </c>
     </row>
@@ -34167,59 +35194,59 @@
         <v>50</v>
       </c>
       <c r="E63" s="11">
+        <f t="shared" si="0"/>
+        <v>41.366730993575999</v>
+      </c>
+      <c r="F63" s="11">
+        <f t="shared" si="1"/>
+        <v>12500.341810860671</v>
+      </c>
+      <c r="G63" s="11">
+        <f t="shared" si="2"/>
+        <v>704878.85360803723</v>
+      </c>
+      <c r="H63" s="11">
+        <f t="shared" si="3"/>
+        <v>3215512.2978489436</v>
+      </c>
+      <c r="I63" s="11">
+        <f t="shared" si="4"/>
+        <v>82973.423267677048</v>
+      </c>
+      <c r="J63" s="11">
+        <f t="shared" si="5"/>
+        <v>1187.8570259493201</v>
+      </c>
+      <c r="K63" s="11">
+        <f t="shared" si="6"/>
+        <v>210.86227521368005</v>
+      </c>
+      <c r="L63" s="11">
+        <f t="shared" si="7"/>
+        <v>17.733193625510001</v>
+      </c>
+      <c r="M63" s="11">
+        <f t="shared" si="8"/>
+        <v>22.009184760751999</v>
+      </c>
+      <c r="N63" s="11">
+        <f t="shared" si="9"/>
+        <v>28.041561207080001</v>
+      </c>
+      <c r="O63" s="11">
+        <f t="shared" si="10"/>
+        <v>34.960291800559993</v>
+      </c>
+      <c r="P63" s="11">
+        <f t="shared" si="11"/>
+        <v>11.241084333950001</v>
+      </c>
+      <c r="Q63" s="11">
+        <f t="shared" si="12"/>
+        <v>1.5371179773200003</v>
+      </c>
+      <c r="R63" s="11">
         <f t="shared" si="13"/>
-        <v>41.366730993575999</v>
-      </c>
-      <c r="F63" s="11">
-        <f t="shared" si="0"/>
-        <v>12500.341810860671</v>
-      </c>
-      <c r="G63" s="11">
-        <f t="shared" si="1"/>
-        <v>704878.85360803723</v>
-      </c>
-      <c r="H63" s="11">
-        <f t="shared" si="2"/>
-        <v>3215512.2978489436</v>
-      </c>
-      <c r="I63" s="11">
-        <f t="shared" si="3"/>
-        <v>82973.423267677048</v>
-      </c>
-      <c r="J63" s="11">
-        <f t="shared" si="4"/>
-        <v>1187.8570259493201</v>
-      </c>
-      <c r="K63" s="11">
-        <f t="shared" si="5"/>
-        <v>210.86227521368005</v>
-      </c>
-      <c r="L63" s="11">
-        <f t="shared" si="6"/>
-        <v>17.733193625510001</v>
-      </c>
-      <c r="M63" s="11">
-        <f t="shared" si="7"/>
-        <v>22.009184760751999</v>
-      </c>
-      <c r="N63" s="11">
-        <f t="shared" si="8"/>
-        <v>28.041561207080001</v>
-      </c>
-      <c r="O63" s="11">
-        <f t="shared" si="9"/>
-        <v>34.960291800559993</v>
-      </c>
-      <c r="P63" s="11">
-        <f t="shared" si="10"/>
-        <v>11.241084333950001</v>
-      </c>
-      <c r="Q63" s="11">
-        <f t="shared" si="11"/>
-        <v>1.5371179773200003</v>
-      </c>
-      <c r="R63" s="11">
-        <f t="shared" si="12"/>
         <v>0.53299641218000016</v>
       </c>
     </row>
@@ -34231,59 +35258,59 @@
         <v>90</v>
       </c>
       <c r="E64" s="11">
+        <f t="shared" si="0"/>
+        <v>3.3990310751999875E-2</v>
+      </c>
+      <c r="F64" s="11">
+        <f t="shared" si="1"/>
+        <v>5.9209586623999666E-2</v>
+      </c>
+      <c r="G64" s="11">
+        <f t="shared" si="2"/>
+        <v>7.1100177056000025E-2</v>
+      </c>
+      <c r="H64" s="11">
+        <f t="shared" si="3"/>
+        <v>5.2010643319999827E-2</v>
+      </c>
+      <c r="I64" s="11">
+        <f t="shared" si="4"/>
+        <v>5.3139850684999823E-2</v>
+      </c>
+      <c r="J64" s="11">
+        <f t="shared" si="5"/>
+        <v>0.12846019760500016</v>
+      </c>
+      <c r="K64" s="11">
+        <f t="shared" si="6"/>
+        <v>0.20063241648999997</v>
+      </c>
+      <c r="L64" s="11">
+        <f t="shared" si="7"/>
+        <v>0.19993022383000003</v>
+      </c>
+      <c r="M64" s="11">
+        <f t="shared" si="8"/>
+        <v>0.13722185053000024</v>
+      </c>
+      <c r="N64" s="11">
+        <f t="shared" si="9"/>
+        <v>9.2814026170999986E-2</v>
+      </c>
+      <c r="O64" s="11">
+        <f t="shared" si="10"/>
+        <v>0.1010210563099998</v>
+      </c>
+      <c r="P64" s="11">
+        <f t="shared" si="11"/>
+        <v>8.962420489999956E-2</v>
+      </c>
+      <c r="Q64" s="11">
+        <f t="shared" si="12"/>
+        <v>8.1170132899999636E-2</v>
+      </c>
+      <c r="R64" s="11">
         <f t="shared" si="13"/>
-        <v>3.3990310751999875E-2</v>
-      </c>
-      <c r="F64" s="11">
-        <f t="shared" si="0"/>
-        <v>5.9209586623999666E-2</v>
-      </c>
-      <c r="G64" s="11">
-        <f t="shared" si="1"/>
-        <v>7.1100177056000025E-2</v>
-      </c>
-      <c r="H64" s="11">
-        <f t="shared" si="2"/>
-        <v>5.2010643319999827E-2</v>
-      </c>
-      <c r="I64" s="11">
-        <f t="shared" si="3"/>
-        <v>5.3139850684999823E-2</v>
-      </c>
-      <c r="J64" s="11">
-        <f t="shared" si="4"/>
-        <v>0.12846019760500016</v>
-      </c>
-      <c r="K64" s="11">
-        <f t="shared" si="5"/>
-        <v>0.20063241648999997</v>
-      </c>
-      <c r="L64" s="11">
-        <f t="shared" si="6"/>
-        <v>0.19993022383000003</v>
-      </c>
-      <c r="M64" s="11">
-        <f t="shared" si="7"/>
-        <v>0.13722185053000024</v>
-      </c>
-      <c r="N64" s="11">
-        <f t="shared" si="8"/>
-        <v>9.2814026170999986E-2</v>
-      </c>
-      <c r="O64" s="11">
-        <f t="shared" si="9"/>
-        <v>0.1010210563099998</v>
-      </c>
-      <c r="P64" s="11">
-        <f t="shared" si="10"/>
-        <v>8.962420489999956E-2</v>
-      </c>
-      <c r="Q64" s="11">
-        <f t="shared" si="11"/>
-        <v>8.1170132899999636E-2</v>
-      </c>
-      <c r="R64" s="11">
-        <f t="shared" si="12"/>
         <v>6.8924546689999922E-2</v>
       </c>
     </row>
@@ -34295,59 +35322,59 @@
         <v>90</v>
       </c>
       <c r="E65" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.0433930193999852E-2</v>
+      </c>
+      <c r="F65" s="11">
+        <f t="shared" si="1"/>
+        <v>1.0386395774000245E-2</v>
+      </c>
+      <c r="G65" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8402919352000335E-2</v>
+      </c>
+      <c r="H65" s="11">
+        <f t="shared" si="3"/>
+        <v>5.6386929680001252E-3</v>
+      </c>
+      <c r="I65" s="11">
+        <f t="shared" si="4"/>
+        <v>2.0521075760000507E-3</v>
+      </c>
+      <c r="J65" s="11">
+        <f t="shared" si="5"/>
+        <v>2.6813857544000008E-2</v>
+      </c>
+      <c r="K65" s="11">
+        <f t="shared" si="6"/>
+        <v>5.6500125007999946E-2</v>
+      </c>
+      <c r="L65" s="11">
+        <f t="shared" si="7"/>
+        <v>6.1542082255999997E-2</v>
+      </c>
+      <c r="M65" s="11">
+        <f t="shared" si="8"/>
+        <v>3.3775180260000148E-2</v>
+      </c>
+      <c r="N65" s="11">
+        <f t="shared" si="9"/>
+        <v>1.8998288119999929E-2</v>
+      </c>
+      <c r="O65" s="11">
+        <f t="shared" si="10"/>
+        <v>1.6981667719999871E-2</v>
+      </c>
+      <c r="P65" s="11">
+        <f t="shared" si="11"/>
+        <v>2.6019248191999855E-2</v>
+      </c>
+      <c r="Q65" s="11">
+        <f t="shared" si="12"/>
+        <v>2.7242155519999978E-2</v>
+      </c>
+      <c r="R65" s="11">
         <f t="shared" si="13"/>
-        <v>-1.0433930193999852E-2</v>
-      </c>
-      <c r="F65" s="11">
-        <f t="shared" si="0"/>
-        <v>1.0386395774000245E-2</v>
-      </c>
-      <c r="G65" s="11">
-        <f t="shared" si="1"/>
-        <v>1.8402919352000335E-2</v>
-      </c>
-      <c r="H65" s="11">
-        <f t="shared" si="2"/>
-        <v>5.6386929680001252E-3</v>
-      </c>
-      <c r="I65" s="11">
-        <f t="shared" si="3"/>
-        <v>2.0521075760000507E-3</v>
-      </c>
-      <c r="J65" s="11">
-        <f t="shared" si="4"/>
-        <v>2.6813857544000008E-2</v>
-      </c>
-      <c r="K65" s="11">
-        <f t="shared" si="5"/>
-        <v>5.6500125007999946E-2</v>
-      </c>
-      <c r="L65" s="11">
-        <f t="shared" si="6"/>
-        <v>6.1542082255999997E-2</v>
-      </c>
-      <c r="M65" s="11">
-        <f t="shared" si="7"/>
-        <v>3.3775180260000148E-2</v>
-      </c>
-      <c r="N65" s="11">
-        <f t="shared" si="8"/>
-        <v>1.8998288119999929E-2</v>
-      </c>
-      <c r="O65" s="11">
-        <f t="shared" si="9"/>
-        <v>1.6981667719999871E-2</v>
-      </c>
-      <c r="P65" s="11">
-        <f t="shared" si="10"/>
-        <v>2.6019248191999855E-2</v>
-      </c>
-      <c r="Q65" s="11">
-        <f t="shared" si="11"/>
-        <v>2.7242155519999978E-2</v>
-      </c>
-      <c r="R65" s="11">
-        <f t="shared" si="12"/>
         <v>2.6121824000000071E-2</v>
       </c>
     </row>
@@ -34359,59 +35386,59 @@
         <v>90</v>
       </c>
       <c r="E66" s="11">
+        <f t="shared" si="0"/>
+        <v>-4.0169718170002255E-3</v>
+      </c>
+      <c r="F66" s="11">
+        <f t="shared" si="1"/>
+        <v>4.0786763158999761E-2</v>
+      </c>
+      <c r="G66" s="11">
+        <f t="shared" si="2"/>
+        <v>9.317853593299974E-2</v>
+      </c>
+      <c r="H66" s="11">
+        <f t="shared" si="3"/>
+        <v>0.10658778892100007</v>
+      </c>
+      <c r="I66" s="11">
+        <f t="shared" si="4"/>
+        <v>0.1070131133329999</v>
+      </c>
+      <c r="J66" s="11">
+        <f t="shared" si="5"/>
+        <v>0.19341361712600014</v>
+      </c>
+      <c r="K66" s="11">
+        <f t="shared" si="6"/>
+        <v>0.27983201742799979</v>
+      </c>
+      <c r="L66" s="11">
+        <f t="shared" si="7"/>
+        <v>0.30122196758000008</v>
+      </c>
+      <c r="M66" s="11">
+        <f t="shared" si="8"/>
+        <v>0.24023807782999995</v>
+      </c>
+      <c r="N66" s="11">
+        <f t="shared" si="9"/>
+        <v>0.22046026995500023</v>
+      </c>
+      <c r="O66" s="11">
+        <f t="shared" si="10"/>
+        <v>0.21065969150000008</v>
+      </c>
+      <c r="P66" s="11">
+        <f t="shared" si="11"/>
+        <v>0.17244743000000007</v>
+      </c>
+      <c r="Q66" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12065954000000012</v>
+      </c>
+      <c r="R66" s="11">
         <f t="shared" si="13"/>
-        <v>-4.0169718170002255E-3</v>
-      </c>
-      <c r="F66" s="11">
-        <f t="shared" si="0"/>
-        <v>4.0786763158999761E-2</v>
-      </c>
-      <c r="G66" s="11">
-        <f t="shared" si="1"/>
-        <v>9.317853593299974E-2</v>
-      </c>
-      <c r="H66" s="11">
-        <f t="shared" si="2"/>
-        <v>0.10658778892100007</v>
-      </c>
-      <c r="I66" s="11">
-        <f t="shared" si="3"/>
-        <v>0.1070131133329999</v>
-      </c>
-      <c r="J66" s="11">
-        <f t="shared" si="4"/>
-        <v>0.19341361712600014</v>
-      </c>
-      <c r="K66" s="11">
-        <f t="shared" si="5"/>
-        <v>0.27983201742799979</v>
-      </c>
-      <c r="L66" s="11">
-        <f t="shared" si="6"/>
-        <v>0.30122196758000008</v>
-      </c>
-      <c r="M66" s="11">
-        <f t="shared" si="7"/>
-        <v>0.24023807782999995</v>
-      </c>
-      <c r="N66" s="11">
-        <f t="shared" si="8"/>
-        <v>0.22046026995500023</v>
-      </c>
-      <c r="O66" s="11">
-        <f t="shared" si="9"/>
-        <v>0.21065969150000008</v>
-      </c>
-      <c r="P66" s="11">
-        <f t="shared" si="10"/>
-        <v>0.17244743000000007</v>
-      </c>
-      <c r="Q66" s="11">
-        <f t="shared" si="11"/>
-        <v>0.12065954000000012</v>
-      </c>
-      <c r="R66" s="11">
-        <f t="shared" si="12"/>
         <v>9.9100185039999955E-2</v>
       </c>
     </row>
@@ -34423,59 +35450,59 @@
         <v>90</v>
       </c>
       <c r="E67" s="11">
+        <f t="shared" si="0"/>
+        <v>5.7651959552000198E-2</v>
+      </c>
+      <c r="F67" s="11">
+        <f t="shared" si="1"/>
+        <v>6.3702838784000404E-2</v>
+      </c>
+      <c r="G67" s="11">
+        <f t="shared" si="2"/>
+        <v>7.1592248684000159E-2</v>
+      </c>
+      <c r="H67" s="11">
+        <f t="shared" si="3"/>
+        <v>5.4661984408000075E-2</v>
+      </c>
+      <c r="I67" s="11">
+        <f t="shared" si="4"/>
+        <v>7.6694448382000013E-2</v>
+      </c>
+      <c r="J67" s="11">
+        <f t="shared" si="5"/>
+        <v>0.18344436424200006</v>
+      </c>
+      <c r="K67" s="11">
+        <f t="shared" si="6"/>
+        <v>0.30955100222799992</v>
+      </c>
+      <c r="L67" s="11">
+        <f t="shared" si="7"/>
+        <v>0.31697376225599982</v>
+      </c>
+      <c r="M67" s="11">
+        <f t="shared" si="8"/>
+        <v>0.22205567471999976</v>
+      </c>
+      <c r="N67" s="11">
+        <f t="shared" si="9"/>
+        <v>0.12014519347999997</v>
+      </c>
+      <c r="O67" s="11">
+        <f t="shared" si="10"/>
+        <v>0.10430821520000011</v>
+      </c>
+      <c r="P67" s="11">
+        <f t="shared" si="11"/>
+        <v>9.5911646480000057E-2</v>
+      </c>
+      <c r="Q67" s="11">
+        <f t="shared" si="12"/>
+        <v>9.6762922639999749E-2</v>
+      </c>
+      <c r="R67" s="11">
         <f t="shared" si="13"/>
-        <v>5.7651959552000198E-2</v>
-      </c>
-      <c r="F67" s="11">
-        <f t="shared" si="0"/>
-        <v>6.3702838784000404E-2</v>
-      </c>
-      <c r="G67" s="11">
-        <f t="shared" si="1"/>
-        <v>7.1592248684000159E-2</v>
-      </c>
-      <c r="H67" s="11">
-        <f t="shared" si="2"/>
-        <v>5.4661984408000075E-2</v>
-      </c>
-      <c r="I67" s="11">
-        <f t="shared" si="3"/>
-        <v>7.6694448382000013E-2</v>
-      </c>
-      <c r="J67" s="11">
-        <f t="shared" si="4"/>
-        <v>0.18344436424200006</v>
-      </c>
-      <c r="K67" s="11">
-        <f t="shared" si="5"/>
-        <v>0.30955100222799992</v>
-      </c>
-      <c r="L67" s="11">
-        <f t="shared" si="6"/>
-        <v>0.31697376225599982</v>
-      </c>
-      <c r="M67" s="11">
-        <f t="shared" si="7"/>
-        <v>0.22205567471999976</v>
-      </c>
-      <c r="N67" s="11">
-        <f t="shared" si="8"/>
-        <v>0.12014519347999997</v>
-      </c>
-      <c r="O67" s="11">
-        <f t="shared" si="9"/>
-        <v>0.10430821520000011</v>
-      </c>
-      <c r="P67" s="11">
-        <f t="shared" si="10"/>
-        <v>9.5911646480000057E-2</v>
-      </c>
-      <c r="Q67" s="11">
-        <f t="shared" si="11"/>
-        <v>9.6762922639999749E-2</v>
-      </c>
-      <c r="R67" s="11">
-        <f t="shared" si="12"/>
         <v>9.4212311192000131E-2</v>
       </c>
     </row>
@@ -34487,59 +35514,59 @@
         <v>90</v>
       </c>
       <c r="E68" s="11">
+        <f t="shared" si="0"/>
+        <v>6.2688296960000667E-3</v>
+      </c>
+      <c r="F68" s="11">
+        <f t="shared" si="1"/>
+        <v>3.3544758272000097E-2</v>
+      </c>
+      <c r="G68" s="11">
+        <f t="shared" si="2"/>
+        <v>5.2695978252000231E-2</v>
+      </c>
+      <c r="H68" s="11">
+        <f t="shared" si="3"/>
+        <v>3.3727549340999863E-2</v>
+      </c>
+      <c r="I68" s="11">
+        <f t="shared" si="4"/>
+        <v>3.4944534584999909E-2</v>
+      </c>
+      <c r="J68" s="11">
+        <f t="shared" si="5"/>
+        <v>0.11259845138000002</v>
+      </c>
+      <c r="K68" s="11">
+        <f t="shared" si="6"/>
+        <v>0.19615768532</v>
+      </c>
+      <c r="L68" s="11">
+        <f t="shared" si="7"/>
+        <v>0.19545440789599988</v>
+      </c>
+      <c r="M68" s="11">
+        <f t="shared" si="8"/>
+        <v>0.12065649214399987</v>
+      </c>
+      <c r="N68" s="11">
+        <f t="shared" si="9"/>
+        <v>8.1566254495999857E-2</v>
+      </c>
+      <c r="O68" s="11">
+        <f t="shared" si="10"/>
+        <v>9.4185764671999905E-2</v>
+      </c>
+      <c r="P68" s="11">
+        <f t="shared" si="11"/>
+        <v>9.3651911352000017E-2</v>
+      </c>
+      <c r="Q68" s="11">
+        <f t="shared" si="12"/>
+        <v>8.2131998486000057E-2</v>
+      </c>
+      <c r="R68" s="11">
         <f t="shared" si="13"/>
-        <v>6.2688296960000667E-3</v>
-      </c>
-      <c r="F68" s="11">
-        <f t="shared" si="0"/>
-        <v>3.3544758272000097E-2</v>
-      </c>
-      <c r="G68" s="11">
-        <f t="shared" si="1"/>
-        <v>5.2695978252000231E-2</v>
-      </c>
-      <c r="H68" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3727549340999863E-2</v>
-      </c>
-      <c r="I68" s="11">
-        <f t="shared" si="3"/>
-        <v>3.4944534584999909E-2</v>
-      </c>
-      <c r="J68" s="11">
-        <f t="shared" si="4"/>
-        <v>0.11259845138000002</v>
-      </c>
-      <c r="K68" s="11">
-        <f t="shared" si="5"/>
-        <v>0.19615768532</v>
-      </c>
-      <c r="L68" s="11">
-        <f t="shared" si="6"/>
-        <v>0.19545440789599988</v>
-      </c>
-      <c r="M68" s="11">
-        <f t="shared" si="7"/>
-        <v>0.12065649214399987</v>
-      </c>
-      <c r="N68" s="11">
-        <f t="shared" si="8"/>
-        <v>8.1566254495999857E-2</v>
-      </c>
-      <c r="O68" s="11">
-        <f t="shared" si="9"/>
-        <v>9.4185764671999905E-2</v>
-      </c>
-      <c r="P68" s="11">
-        <f t="shared" si="10"/>
-        <v>9.3651911352000017E-2</v>
-      </c>
-      <c r="Q68" s="11">
-        <f t="shared" si="11"/>
-        <v>8.2131998486000057E-2</v>
-      </c>
-      <c r="R68" s="11">
-        <f t="shared" si="12"/>
         <v>7.1224678478000181E-2</v>
       </c>
     </row>
@@ -34551,59 +35578,59 @@
         <v>90</v>
       </c>
       <c r="E69" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0008929399999449E-3</v>
+      </c>
+      <c r="F69" s="11">
+        <f t="shared" si="1"/>
+        <v>2.2321342359999941E-2</v>
+      </c>
+      <c r="G69" s="11">
+        <f t="shared" si="2"/>
+        <v>3.6930342120000015E-2</v>
+      </c>
+      <c r="H69" s="11">
+        <f t="shared" si="3"/>
+        <v>2.3827964647999966E-2</v>
+      </c>
+      <c r="I69" s="11">
+        <f t="shared" si="4"/>
+        <v>3.511870234399983E-2</v>
+      </c>
+      <c r="J69" s="11">
+        <f t="shared" si="5"/>
+        <v>0.13648413137599991</v>
+      </c>
+      <c r="K69" s="11">
+        <f t="shared" si="6"/>
+        <v>0.23170245791999999</v>
+      </c>
+      <c r="L69" s="11">
+        <f t="shared" si="7"/>
+        <v>0.24777648688000009</v>
+      </c>
+      <c r="M69" s="11">
+        <f t="shared" si="8"/>
+        <v>0.1769646638400002</v>
+      </c>
+      <c r="N69" s="11">
+        <f t="shared" si="9"/>
+        <v>0.13060267938800019</v>
+      </c>
+      <c r="O69" s="11">
+        <f t="shared" si="10"/>
+        <v>0.11908144462400028</v>
+      </c>
+      <c r="P69" s="11">
+        <f t="shared" si="11"/>
+        <v>9.7746207272000341E-2</v>
+      </c>
+      <c r="Q69" s="11">
+        <f t="shared" si="12"/>
+        <v>7.7927107400000084E-2</v>
+      </c>
+      <c r="R69" s="11">
         <f t="shared" si="13"/>
-        <v>4.0008929399999449E-3</v>
-      </c>
-      <c r="F69" s="11">
-        <f t="shared" si="0"/>
-        <v>2.2321342359999941E-2</v>
-      </c>
-      <c r="G69" s="11">
-        <f t="shared" si="1"/>
-        <v>3.6930342120000015E-2</v>
-      </c>
-      <c r="H69" s="11">
-        <f t="shared" si="2"/>
-        <v>2.3827964647999966E-2</v>
-      </c>
-      <c r="I69" s="11">
-        <f t="shared" si="3"/>
-        <v>3.511870234399983E-2</v>
-      </c>
-      <c r="J69" s="11">
-        <f t="shared" si="4"/>
-        <v>0.13648413137599991</v>
-      </c>
-      <c r="K69" s="11">
-        <f t="shared" si="5"/>
-        <v>0.23170245791999999</v>
-      </c>
-      <c r="L69" s="11">
-        <f t="shared" si="6"/>
-        <v>0.24777648688000009</v>
-      </c>
-      <c r="M69" s="11">
-        <f t="shared" si="7"/>
-        <v>0.1769646638400002</v>
-      </c>
-      <c r="N69" s="11">
-        <f t="shared" si="8"/>
-        <v>0.13060267938800019</v>
-      </c>
-      <c r="O69" s="11">
-        <f t="shared" si="9"/>
-        <v>0.11908144462400028</v>
-      </c>
-      <c r="P69" s="11">
-        <f t="shared" si="10"/>
-        <v>9.7746207272000341E-2</v>
-      </c>
-      <c r="Q69" s="11">
-        <f t="shared" si="11"/>
-        <v>7.7927107400000084E-2</v>
-      </c>
-      <c r="R69" s="11">
-        <f t="shared" si="12"/>
         <v>6.7981198774999863E-2</v>
       </c>
     </row>
@@ -34615,59 +35642,59 @@
         <v>90</v>
       </c>
       <c r="E70" s="11">
+        <f t="shared" si="0"/>
+        <v>3.6760518155000144E-2</v>
+      </c>
+      <c r="F70" s="11">
+        <f t="shared" si="1"/>
+        <v>4.7582439861000081E-2</v>
+      </c>
+      <c r="G70" s="11">
+        <f t="shared" si="2"/>
+        <v>5.4200076852000123E-2</v>
+      </c>
+      <c r="H70" s="11">
+        <f t="shared" si="3"/>
+        <v>2.7219475100000112E-2</v>
+      </c>
+      <c r="I70" s="11">
+        <f t="shared" si="4"/>
+        <v>2.5217293100000093E-2</v>
+      </c>
+      <c r="J70" s="11">
+        <f t="shared" si="5"/>
+        <v>0.15474853340000005</v>
+      </c>
+      <c r="K70" s="11">
+        <f t="shared" si="6"/>
+        <v>0.25696837851200027</v>
+      </c>
+      <c r="L70" s="11">
+        <f t="shared" si="7"/>
+        <v>0.26838308988800041</v>
+      </c>
+      <c r="M70" s="11">
+        <f t="shared" si="8"/>
+        <v>0.16582628308000014</v>
+      </c>
+      <c r="N70" s="11">
+        <f t="shared" si="9"/>
+        <v>0.1145032988000001</v>
+      </c>
+      <c r="O70" s="11">
+        <f t="shared" si="10"/>
+        <v>0.1129934239999999</v>
+      </c>
+      <c r="P70" s="11">
+        <f t="shared" si="11"/>
+        <v>0.10228126400000015</v>
+      </c>
+      <c r="Q70" s="11">
+        <f t="shared" si="12"/>
+        <v>9.0812441599999794E-2</v>
+      </c>
+      <c r="R70" s="11">
         <f t="shared" si="13"/>
-        <v>3.6760518155000144E-2</v>
-      </c>
-      <c r="F70" s="11">
-        <f t="shared" si="0"/>
-        <v>4.7582439861000081E-2</v>
-      </c>
-      <c r="G70" s="11">
-        <f t="shared" si="1"/>
-        <v>5.4200076852000123E-2</v>
-      </c>
-      <c r="H70" s="11">
-        <f t="shared" si="2"/>
-        <v>2.7219475100000112E-2</v>
-      </c>
-      <c r="I70" s="11">
-        <f t="shared" si="3"/>
-        <v>2.5217293100000093E-2</v>
-      </c>
-      <c r="J70" s="11">
-        <f t="shared" si="4"/>
-        <v>0.15474853340000005</v>
-      </c>
-      <c r="K70" s="11">
-        <f t="shared" si="5"/>
-        <v>0.25696837851200027</v>
-      </c>
-      <c r="L70" s="11">
-        <f t="shared" si="6"/>
-        <v>0.26838308988800041</v>
-      </c>
-      <c r="M70" s="11">
-        <f t="shared" si="7"/>
-        <v>0.16582628308000014</v>
-      </c>
-      <c r="N70" s="11">
-        <f t="shared" si="8"/>
-        <v>0.1145032988000001</v>
-      </c>
-      <c r="O70" s="11">
-        <f t="shared" si="9"/>
-        <v>0.1129934239999999</v>
-      </c>
-      <c r="P70" s="11">
-        <f t="shared" si="10"/>
-        <v>0.10228126400000015</v>
-      </c>
-      <c r="Q70" s="11">
-        <f t="shared" si="11"/>
-        <v>9.0812441599999794E-2</v>
-      </c>
-      <c r="R70" s="11">
-        <f t="shared" si="12"/>
         <v>8.4893304319999752E-2</v>
       </c>
     </row>
@@ -34679,59 +35706,59 @@
         <v>90</v>
       </c>
       <c r="E71" s="11">
+        <f t="shared" si="0"/>
+        <v>1.7353482432000078E-2</v>
+      </c>
+      <c r="F71" s="11">
+        <f t="shared" si="1"/>
+        <v>3.0765113279999978E-2</v>
+      </c>
+      <c r="G71" s="11">
+        <f t="shared" si="2"/>
+        <v>3.6112258720000012E-2</v>
+      </c>
+      <c r="H71" s="11">
+        <f t="shared" si="3"/>
+        <v>3.4476722399999993E-2</v>
+      </c>
+      <c r="I71" s="11">
+        <f t="shared" si="4"/>
+        <v>5.2525256640000073E-2</v>
+      </c>
+      <c r="J71" s="11">
+        <f t="shared" si="5"/>
+        <v>0.19291766879999983</v>
+      </c>
+      <c r="K71" s="11">
+        <f t="shared" si="6"/>
+        <v>0.28910549663999974</v>
+      </c>
+      <c r="L71" s="11">
+        <f t="shared" si="7"/>
+        <v>0.29247750287999974</v>
+      </c>
+      <c r="M71" s="11">
+        <f t="shared" si="8"/>
+        <v>0.17782954224799985</v>
+      </c>
+      <c r="N71" s="11">
+        <f t="shared" si="9"/>
+        <v>0.12117826762999973</v>
+      </c>
+      <c r="O71" s="11">
+        <f t="shared" si="10"/>
+        <v>0.12301999441999989</v>
+      </c>
+      <c r="P71" s="11">
+        <f t="shared" si="11"/>
+        <v>0.10791258601999987</v>
+      </c>
+      <c r="Q71" s="11">
+        <f t="shared" si="12"/>
+        <v>9.2480566329999903E-2</v>
+      </c>
+      <c r="R71" s="11">
         <f t="shared" si="13"/>
-        <v>1.7353482432000078E-2</v>
-      </c>
-      <c r="F71" s="11">
-        <f t="shared" si="0"/>
-        <v>3.0765113279999978E-2</v>
-      </c>
-      <c r="G71" s="11">
-        <f t="shared" si="1"/>
-        <v>3.6112258720000012E-2</v>
-      </c>
-      <c r="H71" s="11">
-        <f t="shared" si="2"/>
-        <v>3.4476722399999993E-2</v>
-      </c>
-      <c r="I71" s="11">
-        <f t="shared" si="3"/>
-        <v>5.2525256640000073E-2</v>
-      </c>
-      <c r="J71" s="11">
-        <f t="shared" si="4"/>
-        <v>0.19291766879999983</v>
-      </c>
-      <c r="K71" s="11">
-        <f t="shared" si="5"/>
-        <v>0.28910549663999974</v>
-      </c>
-      <c r="L71" s="11">
-        <f t="shared" si="6"/>
-        <v>0.29247750287999974</v>
-      </c>
-      <c r="M71" s="11">
-        <f t="shared" si="7"/>
-        <v>0.17782954224799985</v>
-      </c>
-      <c r="N71" s="11">
-        <f t="shared" si="8"/>
-        <v>0.12117826762999973</v>
-      </c>
-      <c r="O71" s="11">
-        <f t="shared" si="9"/>
-        <v>0.12301999441999989</v>
-      </c>
-      <c r="P71" s="11">
-        <f t="shared" si="10"/>
-        <v>0.10791258601999987</v>
-      </c>
-      <c r="Q71" s="11">
-        <f t="shared" si="11"/>
-        <v>9.2480566329999903E-2</v>
-      </c>
-      <c r="R71" s="11">
-        <f t="shared" si="12"/>
         <v>7.804203289499978E-2</v>
       </c>
     </row>
@@ -34743,59 +35770,59 @@
         <v>90</v>
       </c>
       <c r="E72" s="11">
+        <f t="shared" si="0"/>
+        <v>0.28214121881599996</v>
+      </c>
+      <c r="F72" s="11">
+        <f t="shared" si="1"/>
+        <v>0.14175269273599977</v>
+      </c>
+      <c r="G72" s="11">
+        <f t="shared" si="2"/>
+        <v>0.11433953484799986</v>
+      </c>
+      <c r="H72" s="11">
+        <f t="shared" si="3"/>
+        <v>0.11111517276799998</v>
+      </c>
+      <c r="I72" s="11">
+        <f t="shared" si="4"/>
+        <v>0.15226358653400007</v>
+      </c>
+      <c r="J72" s="11">
+        <f t="shared" si="5"/>
+        <v>0.25461838775000012</v>
+      </c>
+      <c r="K72" s="11">
+        <f t="shared" si="6"/>
+        <v>0.28471563674999989</v>
+      </c>
+      <c r="L72" s="11">
+        <f t="shared" si="7"/>
+        <v>0.30578839300000005</v>
+      </c>
+      <c r="M72" s="11">
+        <f t="shared" si="8"/>
+        <v>0.24781712807999989</v>
+      </c>
+      <c r="N72" s="11">
+        <f t="shared" si="9"/>
+        <v>0.25111760791999993</v>
+      </c>
+      <c r="O72" s="11">
+        <f t="shared" si="10"/>
+        <v>0.22435079815999992</v>
+      </c>
+      <c r="P72" s="11">
+        <f t="shared" si="11"/>
+        <v>0.17839540481599991</v>
+      </c>
+      <c r="Q72" s="11">
+        <f t="shared" si="12"/>
+        <v>0.16551676651199987</v>
+      </c>
+      <c r="R72" s="11">
         <f t="shared" si="13"/>
-        <v>0.28214121881599996</v>
-      </c>
-      <c r="F72" s="11">
-        <f t="shared" si="0"/>
-        <v>0.14175269273599977</v>
-      </c>
-      <c r="G72" s="11">
-        <f t="shared" si="1"/>
-        <v>0.11433953484799986</v>
-      </c>
-      <c r="H72" s="11">
-        <f t="shared" si="2"/>
-        <v>0.11111517276799998</v>
-      </c>
-      <c r="I72" s="11">
-        <f t="shared" si="3"/>
-        <v>0.15226358653400007</v>
-      </c>
-      <c r="J72" s="11">
-        <f t="shared" si="4"/>
-        <v>0.25461838775000012</v>
-      </c>
-      <c r="K72" s="11">
-        <f t="shared" si="5"/>
-        <v>0.28471563674999989</v>
-      </c>
-      <c r="L72" s="11">
-        <f t="shared" si="6"/>
-        <v>0.30578839300000005</v>
-      </c>
-      <c r="M72" s="11">
-        <f t="shared" si="7"/>
-        <v>0.24781712807999989</v>
-      </c>
-      <c r="N72" s="11">
-        <f t="shared" si="8"/>
-        <v>0.25111760791999993</v>
-      </c>
-      <c r="O72" s="11">
-        <f t="shared" si="9"/>
-        <v>0.22435079815999992</v>
-      </c>
-      <c r="P72" s="11">
-        <f t="shared" si="10"/>
-        <v>0.17839540481599991</v>
-      </c>
-      <c r="Q72" s="11">
-        <f t="shared" si="11"/>
-        <v>0.16551676651199987</v>
-      </c>
-      <c r="R72" s="11">
-        <f t="shared" si="12"/>
         <v>0.15607137997600007</v>
       </c>
     </row>
@@ -34807,59 +35834,59 @@
         <v>90</v>
       </c>
       <c r="E73" s="11">
+        <f t="shared" si="0"/>
+        <v>0.93869393203200024</v>
+      </c>
+      <c r="F73" s="11">
+        <f t="shared" si="1"/>
+        <v>0.4461989296640001</v>
+      </c>
+      <c r="G73" s="11">
+        <f t="shared" si="2"/>
+        <v>0.36964889853799998</v>
+      </c>
+      <c r="H73" s="11">
+        <f t="shared" si="3"/>
+        <v>0.22972758748400013</v>
+      </c>
+      <c r="I73" s="11">
+        <f t="shared" si="4"/>
+        <v>0.212213890096</v>
+      </c>
+      <c r="J73" s="11">
+        <f t="shared" si="5"/>
+        <v>0.35029998435199983</v>
+      </c>
+      <c r="K73" s="11">
+        <f t="shared" si="6"/>
+        <v>0.48317454967999995</v>
+      </c>
+      <c r="L73" s="11">
+        <f t="shared" si="7"/>
+        <v>0.44438633450000009</v>
+      </c>
+      <c r="M73" s="11">
+        <f t="shared" si="8"/>
+        <v>0.35484832324999993</v>
+      </c>
+      <c r="N73" s="11">
+        <f t="shared" si="9"/>
+        <v>0.30502448149999983</v>
+      </c>
+      <c r="O73" s="11">
+        <f t="shared" si="10"/>
+        <v>0.33247288373999995</v>
+      </c>
+      <c r="P73" s="11">
+        <f t="shared" si="11"/>
+        <v>0.28164672033999993</v>
+      </c>
+      <c r="Q73" s="11">
+        <f t="shared" si="12"/>
+        <v>0.27103510996000013</v>
+      </c>
+      <c r="R73" s="11">
         <f t="shared" si="13"/>
-        <v>0.93869393203200024</v>
-      </c>
-      <c r="F73" s="11">
-        <f t="shared" si="0"/>
-        <v>0.4461989296640001</v>
-      </c>
-      <c r="G73" s="11">
-        <f t="shared" si="1"/>
-        <v>0.36964889853799998</v>
-      </c>
-      <c r="H73" s="11">
-        <f t="shared" si="2"/>
-        <v>0.22972758748400013</v>
-      </c>
-      <c r="I73" s="11">
-        <f t="shared" si="3"/>
-        <v>0.212213890096</v>
-      </c>
-      <c r="J73" s="11">
-        <f t="shared" si="4"/>
-        <v>0.35029998435199983</v>
-      </c>
-      <c r="K73" s="11">
-        <f t="shared" si="5"/>
-        <v>0.48317454967999995</v>
-      </c>
-      <c r="L73" s="11">
-        <f t="shared" si="6"/>
-        <v>0.44438633450000009</v>
-      </c>
-      <c r="M73" s="11">
-        <f t="shared" si="7"/>
-        <v>0.35484832324999993</v>
-      </c>
-      <c r="N73" s="11">
-        <f t="shared" si="8"/>
-        <v>0.30502448149999983</v>
-      </c>
-      <c r="O73" s="11">
-        <f t="shared" si="9"/>
-        <v>0.33247288373999995</v>
-      </c>
-      <c r="P73" s="11">
-        <f t="shared" si="10"/>
-        <v>0.28164672033999993</v>
-      </c>
-      <c r="Q73" s="11">
-        <f t="shared" si="11"/>
-        <v>0.27103510996000013</v>
-      </c>
-      <c r="R73" s="11">
-        <f t="shared" si="12"/>
         <v>0.25221621602000011</v>
       </c>
     </row>
@@ -34871,59 +35898,59 @@
         <v>90</v>
       </c>
       <c r="E74" s="11">
+        <f t="shared" si="0"/>
+        <v>0.28891655514999992</v>
+      </c>
+      <c r="F74" s="11">
+        <f t="shared" si="1"/>
+        <v>0.39179063750999998</v>
+      </c>
+      <c r="G74" s="11">
+        <f t="shared" si="2"/>
+        <v>0.48887727774499989</v>
+      </c>
+      <c r="H74" s="11">
+        <f t="shared" si="3"/>
+        <v>0.50468931255499982</v>
+      </c>
+      <c r="I74" s="11">
+        <f t="shared" si="4"/>
+        <v>0.54646109149400002</v>
+      </c>
+      <c r="J74" s="11">
+        <f t="shared" si="5"/>
+        <v>1.313447785478</v>
+      </c>
+      <c r="K74" s="11">
+        <f t="shared" si="6"/>
+        <v>2.1723634340360003</v>
+      </c>
+      <c r="L74" s="11">
+        <f t="shared" si="7"/>
+        <v>3.2059416192679997</v>
+      </c>
+      <c r="M74" s="11">
+        <f t="shared" si="8"/>
+        <v>2.2934214629720002</v>
+      </c>
+      <c r="N74" s="11">
+        <f t="shared" si="9"/>
+        <v>1.7946385787239998</v>
+      </c>
+      <c r="O74" s="11">
+        <f t="shared" si="10"/>
+        <v>1.1466575382679998</v>
+      </c>
+      <c r="P74" s="11">
+        <f t="shared" si="11"/>
+        <v>0.81155556098000003</v>
+      </c>
+      <c r="Q74" s="11">
+        <f t="shared" si="12"/>
+        <v>0.53453979404000007</v>
+      </c>
+      <c r="R74" s="11">
         <f t="shared" si="13"/>
-        <v>0.28891655514999992</v>
-      </c>
-      <c r="F74" s="11">
-        <f t="shared" si="0"/>
-        <v>0.39179063750999998</v>
-      </c>
-      <c r="G74" s="11">
-        <f t="shared" si="1"/>
-        <v>0.48887727774499989</v>
-      </c>
-      <c r="H74" s="11">
-        <f t="shared" si="2"/>
-        <v>0.50468931255499982</v>
-      </c>
-      <c r="I74" s="11">
-        <f t="shared" si="3"/>
-        <v>0.54646109149400002</v>
-      </c>
-      <c r="J74" s="11">
-        <f t="shared" si="4"/>
-        <v>1.313447785478</v>
-      </c>
-      <c r="K74" s="11">
-        <f t="shared" si="5"/>
-        <v>2.1723634340360003</v>
-      </c>
-      <c r="L74" s="11">
-        <f t="shared" si="6"/>
-        <v>3.2059416192679997</v>
-      </c>
-      <c r="M74" s="11">
-        <f t="shared" si="7"/>
-        <v>2.2934214629720002</v>
-      </c>
-      <c r="N74" s="11">
-        <f t="shared" si="8"/>
-        <v>1.7946385787239998</v>
-      </c>
-      <c r="O74" s="11">
-        <f t="shared" si="9"/>
-        <v>1.1466575382679998</v>
-      </c>
-      <c r="P74" s="11">
-        <f t="shared" si="10"/>
-        <v>0.81155556098000003</v>
-      </c>
-      <c r="Q74" s="11">
-        <f t="shared" si="11"/>
-        <v>0.53453979404000007</v>
-      </c>
-      <c r="R74" s="11">
-        <f t="shared" si="12"/>
         <v>0.39580368685999989</v>
       </c>
     </row>
@@ -34935,59 +35962,59 @@
         <v>90</v>
       </c>
       <c r="E75" s="11">
+        <f t="shared" si="0"/>
+        <v>0.31075992051199997</v>
+      </c>
+      <c r="F75" s="11">
+        <f t="shared" si="1"/>
+        <v>0.30437076454400014</v>
+      </c>
+      <c r="G75" s="11">
+        <f t="shared" si="2"/>
+        <v>0.20137611603200001</v>
+      </c>
+      <c r="H75" s="11">
+        <f t="shared" si="3"/>
+        <v>0.19332519641599988</v>
+      </c>
+      <c r="I75" s="11">
+        <f t="shared" si="4"/>
+        <v>0.214457933504</v>
+      </c>
+      <c r="J75" s="11">
+        <f t="shared" si="5"/>
+        <v>0.32629921286399988</v>
+      </c>
+      <c r="K75" s="11">
+        <f t="shared" si="6"/>
+        <v>0.42572194246399997</v>
+      </c>
+      <c r="L75" s="11">
+        <f t="shared" si="7"/>
+        <v>0.43773052231999987</v>
+      </c>
+      <c r="M75" s="11">
+        <f t="shared" si="8"/>
+        <v>0.39298501879999992</v>
+      </c>
+      <c r="N75" s="11">
+        <f t="shared" si="9"/>
+        <v>0.3395581178</v>
+      </c>
+      <c r="O75" s="11">
+        <f t="shared" si="10"/>
+        <v>0.33820564976000012</v>
+      </c>
+      <c r="P75" s="11">
+        <f t="shared" si="11"/>
+        <v>0.29702085497600006</v>
+      </c>
+      <c r="Q75" s="11">
+        <f t="shared" si="12"/>
+        <v>0.25963392315199996</v>
+      </c>
+      <c r="R75" s="11">
         <f t="shared" si="13"/>
-        <v>0.31075992051199997</v>
-      </c>
-      <c r="F75" s="11">
-        <f t="shared" si="0"/>
-        <v>0.30437076454400014</v>
-      </c>
-      <c r="G75" s="11">
-        <f t="shared" si="1"/>
-        <v>0.20137611603200001</v>
-      </c>
-      <c r="H75" s="11">
-        <f t="shared" si="2"/>
-        <v>0.19332519641599988</v>
-      </c>
-      <c r="I75" s="11">
-        <f t="shared" si="3"/>
-        <v>0.214457933504</v>
-      </c>
-      <c r="J75" s="11">
-        <f t="shared" si="4"/>
-        <v>0.32629921286399988</v>
-      </c>
-      <c r="K75" s="11">
-        <f t="shared" si="5"/>
-        <v>0.42572194246399997</v>
-      </c>
-      <c r="L75" s="11">
-        <f t="shared" si="6"/>
-        <v>0.43773052231999987</v>
-      </c>
-      <c r="M75" s="11">
-        <f t="shared" si="7"/>
-        <v>0.39298501879999992</v>
-      </c>
-      <c r="N75" s="11">
-        <f t="shared" si="8"/>
-        <v>0.3395581178</v>
-      </c>
-      <c r="O75" s="11">
-        <f t="shared" si="9"/>
-        <v>0.33820564976000012</v>
-      </c>
-      <c r="P75" s="11">
-        <f t="shared" si="10"/>
-        <v>0.29702085497600006</v>
-      </c>
-      <c r="Q75" s="11">
-        <f t="shared" si="11"/>
-        <v>0.25963392315199996</v>
-      </c>
-      <c r="R75" s="11">
-        <f t="shared" si="12"/>
         <v>0.23243675557199994</v>
       </c>
     </row>
@@ -34999,59 +36026,59 @@
         <v>90</v>
       </c>
       <c r="E76" s="11">
+        <f t="shared" si="0"/>
+        <v>5.0828676320000099E-2</v>
+      </c>
+      <c r="F76" s="11">
+        <f t="shared" si="1"/>
+        <v>5.7769283704999896E-2</v>
+      </c>
+      <c r="G76" s="11">
+        <f t="shared" si="2"/>
+        <v>6.6997934450000018E-2</v>
+      </c>
+      <c r="H76" s="11">
+        <f t="shared" si="3"/>
+        <v>7.6769555119999833E-2</v>
+      </c>
+      <c r="I76" s="11">
+        <f t="shared" si="4"/>
+        <v>6.4115324719999922E-2</v>
+      </c>
+      <c r="J76" s="11">
+        <f t="shared" si="5"/>
+        <v>5.43945433280002E-2</v>
+      </c>
+      <c r="K76" s="11">
+        <f t="shared" si="6"/>
+        <v>3.1347668064000134E-2</v>
+      </c>
+      <c r="L76" s="11">
+        <f t="shared" si="7"/>
+        <v>2.4499952896000154E-2</v>
+      </c>
+      <c r="M76" s="11">
+        <f t="shared" si="8"/>
+        <v>5.3081628800000225E-3</v>
+      </c>
+      <c r="N76" s="11">
+        <f t="shared" si="9"/>
+        <v>1.3030502119999898E-2</v>
+      </c>
+      <c r="O76" s="11">
+        <f t="shared" si="10"/>
+        <v>2.1418524034999775E-2</v>
+      </c>
+      <c r="P76" s="11">
+        <f t="shared" si="11"/>
+        <v>3.3669420874999911E-2</v>
+      </c>
+      <c r="Q76" s="11">
+        <f t="shared" si="12"/>
+        <v>3.9195423125000017E-2</v>
+      </c>
+      <c r="R76" s="11">
         <f t="shared" si="13"/>
-        <v>5.0828676320000099E-2</v>
-      </c>
-      <c r="F76" s="11">
-        <f t="shared" si="0"/>
-        <v>5.7769283704999896E-2</v>
-      </c>
-      <c r="G76" s="11">
-        <f t="shared" si="1"/>
-        <v>6.6997934450000018E-2</v>
-      </c>
-      <c r="H76" s="11">
-        <f t="shared" si="2"/>
-        <v>7.6769555119999833E-2</v>
-      </c>
-      <c r="I76" s="11">
-        <f t="shared" si="3"/>
-        <v>6.4115324719999922E-2</v>
-      </c>
-      <c r="J76" s="11">
-        <f t="shared" si="4"/>
-        <v>5.43945433280002E-2</v>
-      </c>
-      <c r="K76" s="11">
-        <f t="shared" si="5"/>
-        <v>3.1347668064000134E-2</v>
-      </c>
-      <c r="L76" s="11">
-        <f t="shared" si="6"/>
-        <v>2.4499952896000154E-2</v>
-      </c>
-      <c r="M76" s="11">
-        <f t="shared" si="7"/>
-        <v>5.3081628800000225E-3</v>
-      </c>
-      <c r="N76" s="11">
-        <f t="shared" si="8"/>
-        <v>1.3030502119999898E-2</v>
-      </c>
-      <c r="O76" s="11">
-        <f t="shared" si="9"/>
-        <v>2.1418524034999775E-2</v>
-      </c>
-      <c r="P76" s="11">
-        <f t="shared" si="10"/>
-        <v>3.3669420874999911E-2</v>
-      </c>
-      <c r="Q76" s="11">
-        <f t="shared" si="11"/>
-        <v>3.9195423125000017E-2</v>
-      </c>
-      <c r="R76" s="11">
-        <f t="shared" si="12"/>
         <v>4.5056127499999876E-2</v>
       </c>
     </row>
@@ -35063,59 +36090,59 @@
         <v>90</v>
       </c>
       <c r="E77" s="11">
+        <f t="shared" si="0"/>
+        <v>0.13769476398500013</v>
+      </c>
+      <c r="F77" s="11">
+        <f t="shared" si="1"/>
+        <v>0.12728405982500024</v>
+      </c>
+      <c r="G77" s="11">
+        <f t="shared" si="2"/>
+        <v>0.11407244102000025</v>
+      </c>
+      <c r="H77" s="11">
+        <f t="shared" si="3"/>
+        <v>0.14954421428000009</v>
+      </c>
+      <c r="I77" s="11">
+        <f t="shared" si="4"/>
+        <v>0.16270397969599992</v>
+      </c>
+      <c r="J77" s="11">
+        <f t="shared" si="5"/>
+        <v>0.19599775929199992</v>
+      </c>
+      <c r="K77" s="11">
+        <f t="shared" si="6"/>
+        <v>0.18511689428999989</v>
+      </c>
+      <c r="L77" s="11">
+        <f t="shared" si="7"/>
+        <v>0.18297525257499991</v>
+      </c>
+      <c r="M77" s="11">
+        <f t="shared" si="8"/>
+        <v>0.13319027850000009</v>
+      </c>
+      <c r="N77" s="11">
+        <f t="shared" si="9"/>
+        <v>0.12460956649999999</v>
+      </c>
+      <c r="O77" s="11">
+        <f t="shared" si="10"/>
+        <v>0.13382504270000006</v>
+      </c>
+      <c r="P77" s="11">
+        <f t="shared" si="11"/>
+        <v>0.15545869077500019</v>
+      </c>
+      <c r="Q77" s="11">
+        <f t="shared" si="12"/>
+        <v>0.15391587516500005</v>
+      </c>
+      <c r="R77" s="11">
         <f t="shared" si="13"/>
-        <v>0.13769476398500013</v>
-      </c>
-      <c r="F77" s="11">
-        <f t="shared" si="0"/>
-        <v>0.12728405982500024</v>
-      </c>
-      <c r="G77" s="11">
-        <f t="shared" si="1"/>
-        <v>0.11407244102000025</v>
-      </c>
-      <c r="H77" s="11">
-        <f t="shared" si="2"/>
-        <v>0.14954421428000009</v>
-      </c>
-      <c r="I77" s="11">
-        <f t="shared" si="3"/>
-        <v>0.16270397969599992</v>
-      </c>
-      <c r="J77" s="11">
-        <f t="shared" si="4"/>
-        <v>0.19599775929199992</v>
-      </c>
-      <c r="K77" s="11">
-        <f t="shared" si="5"/>
-        <v>0.18511689428999989</v>
-      </c>
-      <c r="L77" s="11">
-        <f t="shared" si="6"/>
-        <v>0.18297525257499991</v>
-      </c>
-      <c r="M77" s="11">
-        <f t="shared" si="7"/>
-        <v>0.13319027850000009</v>
-      </c>
-      <c r="N77" s="11">
-        <f t="shared" si="8"/>
-        <v>0.12460956649999999</v>
-      </c>
-      <c r="O77" s="11">
-        <f t="shared" si="9"/>
-        <v>0.13382504270000006</v>
-      </c>
-      <c r="P77" s="11">
-        <f t="shared" si="10"/>
-        <v>0.15545869077500019</v>
-      </c>
-      <c r="Q77" s="11">
-        <f t="shared" si="11"/>
-        <v>0.15391587516500005</v>
-      </c>
-      <c r="R77" s="11">
-        <f t="shared" si="12"/>
         <v>0.14377371691999996</v>
       </c>
     </row>
@@ -35127,59 +36154,59 @@
         <v>90</v>
       </c>
       <c r="E78" s="11">
+        <f t="shared" si="0"/>
+        <v>3.6596126078000335E-2</v>
+      </c>
+      <c r="F78" s="11">
+        <f t="shared" si="1"/>
+        <v>4.4521645064000248E-2</v>
+      </c>
+      <c r="G78" s="11">
+        <f t="shared" si="2"/>
+        <v>3.8418171056000094E-2</v>
+      </c>
+      <c r="H78" s="11">
+        <f t="shared" si="3"/>
+        <v>2.4156983696000056E-2</v>
+      </c>
+      <c r="I78" s="11">
+        <f t="shared" si="4"/>
+        <v>3.4451033000000075E-2</v>
+      </c>
+      <c r="J78" s="11">
+        <f t="shared" si="5"/>
+        <v>8.2989231499999816E-2</v>
+      </c>
+      <c r="K78" s="11">
+        <f t="shared" si="6"/>
+        <v>0.1159507099999999</v>
+      </c>
+      <c r="L78" s="11">
+        <f t="shared" si="7"/>
+        <v>0.11399099168000015</v>
+      </c>
+      <c r="M78" s="11">
+        <f t="shared" si="8"/>
+        <v>8.2507946240000241E-2</v>
+      </c>
+      <c r="N78" s="11">
+        <f t="shared" si="9"/>
+        <v>7.3208408864000152E-2</v>
+      </c>
+      <c r="O78" s="11">
+        <f t="shared" si="10"/>
+        <v>7.2264421796000011E-2</v>
+      </c>
+      <c r="P78" s="11">
+        <f t="shared" si="11"/>
+        <v>7.0479414435000054E-2</v>
+      </c>
+      <c r="Q78" s="11">
+        <f t="shared" si="12"/>
+        <v>6.1828865180000081E-2</v>
+      </c>
+      <c r="R78" s="11">
         <f t="shared" si="13"/>
-        <v>3.6596126078000335E-2</v>
-      </c>
-      <c r="F78" s="11">
-        <f t="shared" si="0"/>
-        <v>4.4521645064000248E-2</v>
-      </c>
-      <c r="G78" s="11">
-        <f t="shared" si="1"/>
-        <v>3.8418171056000094E-2</v>
-      </c>
-      <c r="H78" s="11">
-        <f t="shared" si="2"/>
-        <v>2.4156983696000056E-2</v>
-      </c>
-      <c r="I78" s="11">
-        <f t="shared" si="3"/>
-        <v>3.4451033000000075E-2</v>
-      </c>
-      <c r="J78" s="11">
-        <f t="shared" si="4"/>
-        <v>8.2989231499999816E-2</v>
-      </c>
-      <c r="K78" s="11">
-        <f t="shared" si="5"/>
-        <v>0.1159507099999999</v>
-      </c>
-      <c r="L78" s="11">
-        <f t="shared" si="6"/>
-        <v>0.11399099168000015</v>
-      </c>
-      <c r="M78" s="11">
-        <f t="shared" si="7"/>
-        <v>8.2507946240000241E-2</v>
-      </c>
-      <c r="N78" s="11">
-        <f t="shared" si="8"/>
-        <v>7.3208408864000152E-2</v>
-      </c>
-      <c r="O78" s="11">
-        <f t="shared" si="9"/>
-        <v>7.2264421796000011E-2</v>
-      </c>
-      <c r="P78" s="11">
-        <f t="shared" si="10"/>
-        <v>7.0479414435000054E-2</v>
-      </c>
-      <c r="Q78" s="11">
-        <f t="shared" si="11"/>
-        <v>6.1828865180000081E-2</v>
-      </c>
-      <c r="R78" s="11">
-        <f t="shared" si="12"/>
         <v>5.8089665419999825E-2</v>
       </c>
     </row>
@@ -35191,59 +36218,59 @@
         <v>90</v>
       </c>
       <c r="E79" s="11">
+        <f t="shared" si="0"/>
+        <v>0.17082572655200012</v>
+      </c>
+      <c r="F79" s="11">
+        <f t="shared" si="1"/>
+        <v>0.17093767087999989</v>
+      </c>
+      <c r="G79" s="11">
+        <f t="shared" si="2"/>
+        <v>0.14670833607999989</v>
+      </c>
+      <c r="H79" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12492643207999987</v>
+      </c>
+      <c r="I79" s="11">
+        <f t="shared" si="4"/>
+        <v>0.12438870433999982</v>
+      </c>
+      <c r="J79" s="11">
+        <f t="shared" si="5"/>
+        <v>0.15397788076999985</v>
+      </c>
+      <c r="K79" s="11">
+        <f t="shared" si="6"/>
+        <v>0.18313735670000009</v>
+      </c>
+      <c r="L79" s="11">
+        <f t="shared" si="7"/>
+        <v>0.18177937981999981</v>
+      </c>
+      <c r="M79" s="11">
+        <f t="shared" si="8"/>
+        <v>0.14152412113999979</v>
+      </c>
+      <c r="N79" s="11">
+        <f t="shared" si="9"/>
+        <v>0.1248162610100001</v>
+      </c>
+      <c r="O79" s="11">
+        <f t="shared" si="10"/>
+        <v>0.12417000059000016</v>
+      </c>
+      <c r="P79" s="11">
+        <f t="shared" si="11"/>
+        <v>0.12438782078000021</v>
+      </c>
+      <c r="Q79" s="11">
+        <f t="shared" si="12"/>
+        <v>0.11005685957600009</v>
+      </c>
+      <c r="R79" s="11">
         <f t="shared" si="13"/>
-        <v>0.17082572655200012</v>
-      </c>
-      <c r="F79" s="11">
-        <f t="shared" si="0"/>
-        <v>0.17093767087999989</v>
-      </c>
-      <c r="G79" s="11">
-        <f t="shared" si="1"/>
-        <v>0.14670833607999989</v>
-      </c>
-      <c r="H79" s="11">
-        <f t="shared" si="2"/>
-        <v>0.12492643207999987</v>
-      </c>
-      <c r="I79" s="11">
-        <f t="shared" si="3"/>
-        <v>0.12438870433999982</v>
-      </c>
-      <c r="J79" s="11">
-        <f t="shared" si="4"/>
-        <v>0.15397788076999985</v>
-      </c>
-      <c r="K79" s="11">
-        <f t="shared" si="5"/>
-        <v>0.18313735670000009</v>
-      </c>
-      <c r="L79" s="11">
-        <f t="shared" si="6"/>
-        <v>0.18177937981999981</v>
-      </c>
-      <c r="M79" s="11">
-        <f t="shared" si="7"/>
-        <v>0.14152412113999979</v>
-      </c>
-      <c r="N79" s="11">
-        <f t="shared" si="8"/>
-        <v>0.1248162610100001</v>
-      </c>
-      <c r="O79" s="11">
-        <f t="shared" si="9"/>
-        <v>0.12417000059000016</v>
-      </c>
-      <c r="P79" s="11">
-        <f t="shared" si="10"/>
-        <v>0.12438782078000021</v>
-      </c>
-      <c r="Q79" s="11">
-        <f t="shared" si="11"/>
-        <v>0.11005685957600009</v>
-      </c>
-      <c r="R79" s="11">
-        <f t="shared" si="12"/>
         <v>9.6336697183999842E-2</v>
       </c>
     </row>
@@ -35255,59 +36282,59 @@
         <v>90</v>
       </c>
       <c r="E80" s="11">
+        <f t="shared" si="0"/>
+        <v>3.9997758800000005E-2</v>
+      </c>
+      <c r="F80" s="11">
+        <f t="shared" si="1"/>
+        <v>4.2353011700000165E-2</v>
+      </c>
+      <c r="G80" s="11">
+        <f t="shared" si="2"/>
+        <v>2.8713406175000067E-2</v>
+      </c>
+      <c r="H80" s="11">
+        <f t="shared" si="3"/>
+        <v>2.5139711960000088E-2</v>
+      </c>
+      <c r="I80" s="11">
+        <f t="shared" si="4"/>
+        <v>2.0607706160000072E-2</v>
+      </c>
+      <c r="J80" s="11">
+        <f t="shared" si="5"/>
+        <v>8.52160097600001E-2</v>
+      </c>
+      <c r="K80" s="11">
+        <f t="shared" si="6"/>
+        <v>0.14671878959600004</v>
+      </c>
+      <c r="L80" s="11">
+        <f t="shared" si="7"/>
+        <v>0.14275834380600005</v>
+      </c>
+      <c r="M80" s="11">
+        <f t="shared" si="8"/>
+        <v>7.8902730369999841E-2</v>
+      </c>
+      <c r="N80" s="11">
+        <f t="shared" si="9"/>
+        <v>2.3071115799999875E-2</v>
+      </c>
+      <c r="O80" s="11">
+        <f t="shared" si="10"/>
+        <v>2.519850400000001E-2</v>
+      </c>
+      <c r="P80" s="11">
+        <f t="shared" si="11"/>
+        <v>3.8229825600000211E-2</v>
+      </c>
+      <c r="Q80" s="11">
+        <f t="shared" si="12"/>
+        <v>4.9272627919999978E-2</v>
+      </c>
+      <c r="R80" s="11">
         <f t="shared" si="13"/>
-        <v>3.9997758800000005E-2</v>
-      </c>
-      <c r="F80" s="11">
-        <f t="shared" si="0"/>
-        <v>4.2353011700000165E-2</v>
-      </c>
-      <c r="G80" s="11">
-        <f t="shared" si="1"/>
-        <v>2.8713406175000067E-2</v>
-      </c>
-      <c r="H80" s="11">
-        <f t="shared" si="2"/>
-        <v>2.5139711960000088E-2</v>
-      </c>
-      <c r="I80" s="11">
-        <f t="shared" si="3"/>
-        <v>2.0607706160000072E-2</v>
-      </c>
-      <c r="J80" s="11">
-        <f t="shared" si="4"/>
-        <v>8.52160097600001E-2</v>
-      </c>
-      <c r="K80" s="11">
-        <f t="shared" si="5"/>
-        <v>0.14671878959600004</v>
-      </c>
-      <c r="L80" s="11">
-        <f t="shared" si="6"/>
-        <v>0.14275834380600005</v>
-      </c>
-      <c r="M80" s="11">
-        <f t="shared" si="7"/>
-        <v>7.8902730369999841E-2</v>
-      </c>
-      <c r="N80" s="11">
-        <f t="shared" si="8"/>
-        <v>2.3071115799999875E-2</v>
-      </c>
-      <c r="O80" s="11">
-        <f t="shared" si="9"/>
-        <v>2.519850400000001E-2</v>
-      </c>
-      <c r="P80" s="11">
-        <f t="shared" si="10"/>
-        <v>3.8229825600000211E-2</v>
-      </c>
-      <c r="Q80" s="11">
-        <f t="shared" si="11"/>
-        <v>4.9272627919999978E-2</v>
-      </c>
-      <c r="R80" s="11">
-        <f t="shared" si="12"/>
         <v>5.4145732021999793E-2</v>
       </c>
     </row>
@@ -35319,59 +36346,59 @@
         <v>90</v>
       </c>
       <c r="E81" s="11">
+        <f t="shared" si="0"/>
+        <v>0.14425691520499995</v>
+      </c>
+      <c r="F81" s="11">
+        <f t="shared" si="1"/>
+        <v>0.17110357244299967</v>
+      </c>
+      <c r="G81" s="11">
+        <f t="shared" si="2"/>
+        <v>0.20602309419199982</v>
+      </c>
+      <c r="H81" s="11">
+        <f t="shared" si="3"/>
+        <v>0.20968777361599988</v>
+      </c>
+      <c r="I81" s="11">
+        <f t="shared" si="4"/>
+        <v>0.19165123985599974</v>
+      </c>
+      <c r="J81" s="11">
+        <f t="shared" si="5"/>
+        <v>0.20940541406299995</v>
+      </c>
+      <c r="K81" s="11">
+        <f t="shared" si="6"/>
+        <v>0.25165388493199981</v>
+      </c>
+      <c r="L81" s="11">
+        <f t="shared" si="7"/>
+        <v>0.26704646889199979</v>
+      </c>
+      <c r="M81" s="11">
+        <f t="shared" si="8"/>
+        <v>0.23241940262000016</v>
+      </c>
+      <c r="N81" s="11">
+        <f t="shared" si="9"/>
+        <v>0.18743812365500001</v>
+      </c>
+      <c r="O81" s="11">
+        <f t="shared" si="10"/>
+        <v>0.16080648645500006</v>
+      </c>
+      <c r="P81" s="11">
+        <f t="shared" si="11"/>
+        <v>0.14637215805199988</v>
+      </c>
+      <c r="Q81" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12678163413199983</v>
+      </c>
+      <c r="R81" s="11">
         <f t="shared" si="13"/>
-        <v>0.14425691520499995</v>
-      </c>
-      <c r="F81" s="11">
-        <f t="shared" si="0"/>
-        <v>0.17110357244299967</v>
-      </c>
-      <c r="G81" s="11">
-        <f t="shared" si="1"/>
-        <v>0.20602309419199982</v>
-      </c>
-      <c r="H81" s="11">
-        <f t="shared" si="2"/>
-        <v>0.20968777361599988</v>
-      </c>
-      <c r="I81" s="11">
-        <f t="shared" si="3"/>
-        <v>0.19165123985599974</v>
-      </c>
-      <c r="J81" s="11">
-        <f t="shared" si="4"/>
-        <v>0.20940541406299995</v>
-      </c>
-      <c r="K81" s="11">
-        <f t="shared" si="5"/>
-        <v>0.25165388493199981</v>
-      </c>
-      <c r="L81" s="11">
-        <f t="shared" si="6"/>
-        <v>0.26704646889199979</v>
-      </c>
-      <c r="M81" s="11">
-        <f t="shared" si="7"/>
-        <v>0.23241940262000016</v>
-      </c>
-      <c r="N81" s="11">
-        <f t="shared" si="8"/>
-        <v>0.18743812365500001</v>
-      </c>
-      <c r="O81" s="11">
-        <f t="shared" si="9"/>
-        <v>0.16080648645500006</v>
-      </c>
-      <c r="P81" s="11">
-        <f t="shared" si="10"/>
-        <v>0.14637215805199988</v>
-      </c>
-      <c r="Q81" s="11">
-        <f t="shared" si="11"/>
-        <v>0.12678163413199983</v>
-      </c>
-      <c r="R81" s="11">
-        <f t="shared" si="12"/>
         <v>0.10707022613599992</v>
       </c>
     </row>
@@ -35383,59 +36410,59 @@
         <v>90</v>
       </c>
       <c r="E82" s="11">
+        <f t="shared" si="0"/>
+        <v>1.0625374116000064E-2</v>
+      </c>
+      <c r="F82" s="11">
+        <f t="shared" si="1"/>
+        <v>3.4729048632000215E-2</v>
+      </c>
+      <c r="G82" s="11">
+        <f t="shared" si="2"/>
+        <v>4.6252568687999984E-2</v>
+      </c>
+      <c r="H82" s="11">
+        <f t="shared" si="3"/>
+        <v>2.1849578552000315E-2</v>
+      </c>
+      <c r="I82" s="11">
+        <f t="shared" si="4"/>
+        <v>3.4605121748000123E-2</v>
+      </c>
+      <c r="J82" s="11">
+        <f t="shared" si="5"/>
+        <v>0.11201058531199992</v>
+      </c>
+      <c r="K82" s="11">
+        <f t="shared" si="6"/>
+        <v>0.15374166687999979</v>
+      </c>
+      <c r="L82" s="11">
+        <f t="shared" si="7"/>
+        <v>0.15217362656</v>
+      </c>
+      <c r="M82" s="11">
+        <f t="shared" si="8"/>
+        <v>9.2288679019999931E-2</v>
+      </c>
+      <c r="N82" s="11">
+        <f t="shared" si="9"/>
+        <v>9.7464901966999751E-2</v>
+      </c>
+      <c r="O82" s="11">
+        <f t="shared" si="10"/>
+        <v>0.10002533335099972</v>
+      </c>
+      <c r="P82" s="11">
+        <f t="shared" si="11"/>
+        <v>9.1027171114999916E-2</v>
+      </c>
+      <c r="Q82" s="11">
+        <f t="shared" si="12"/>
+        <v>7.0128681649999747E-2</v>
+      </c>
+      <c r="R82" s="11">
         <f t="shared" si="13"/>
-        <v>1.0625374116000064E-2</v>
-      </c>
-      <c r="F82" s="11">
-        <f t="shared" si="0"/>
-        <v>3.4729048632000215E-2</v>
-      </c>
-      <c r="G82" s="11">
-        <f t="shared" si="1"/>
-        <v>4.6252568687999984E-2</v>
-      </c>
-      <c r="H82" s="11">
-        <f t="shared" si="2"/>
-        <v>2.1849578552000315E-2</v>
-      </c>
-      <c r="I82" s="11">
-        <f t="shared" si="3"/>
-        <v>3.4605121748000123E-2</v>
-      </c>
-      <c r="J82" s="11">
-        <f t="shared" si="4"/>
-        <v>0.11201058531199992</v>
-      </c>
-      <c r="K82" s="11">
-        <f t="shared" si="5"/>
-        <v>0.15374166687999979</v>
-      </c>
-      <c r="L82" s="11">
-        <f t="shared" si="6"/>
-        <v>0.15217362656</v>
-      </c>
-      <c r="M82" s="11">
-        <f t="shared" si="7"/>
-        <v>9.2288679019999931E-2</v>
-      </c>
-      <c r="N82" s="11">
-        <f t="shared" si="8"/>
-        <v>9.7464901966999751E-2</v>
-      </c>
-      <c r="O82" s="11">
-        <f t="shared" si="9"/>
-        <v>0.10002533335099972</v>
-      </c>
-      <c r="P82" s="11">
-        <f t="shared" si="10"/>
-        <v>9.1027171114999916E-2</v>
-      </c>
-      <c r="Q82" s="11">
-        <f t="shared" si="11"/>
-        <v>7.0128681649999747E-2</v>
-      </c>
-      <c r="R82" s="11">
-        <f t="shared" si="12"/>
         <v>5.8919885449999931E-2</v>
       </c>
     </row>
@@ -35447,59 +36474,59 @@
         <v>90</v>
       </c>
       <c r="E83" s="11">
+        <f t="shared" si="0"/>
+        <v>2.7312549184000057E-2</v>
+      </c>
+      <c r="F83" s="11">
+        <f t="shared" si="1"/>
+        <v>3.4058408128000206E-2</v>
+      </c>
+      <c r="G83" s="11">
+        <f t="shared" si="2"/>
+        <v>3.0564967560000156E-2</v>
+      </c>
+      <c r="H83" s="11">
+        <f t="shared" si="3"/>
+        <v>1.3517417879999938E-2</v>
+      </c>
+      <c r="I83" s="11">
+        <f t="shared" si="4"/>
+        <v>1.1213286160000058E-2</v>
+      </c>
+      <c r="J83" s="11">
+        <f t="shared" si="5"/>
+        <v>8.9852006320000122E-2</v>
+      </c>
+      <c r="K83" s="11">
+        <f t="shared" si="6"/>
+        <v>0.14855648964000001</v>
+      </c>
+      <c r="L83" s="11">
+        <f t="shared" si="7"/>
+        <v>0.16824147801999989</v>
+      </c>
+      <c r="M83" s="11">
+        <f t="shared" si="8"/>
+        <v>0.10437184679799993</v>
+      </c>
+      <c r="N83" s="11">
+        <f t="shared" si="9"/>
+        <v>8.2234048994999975E-2</v>
+      </c>
+      <c r="O83" s="11">
+        <f t="shared" si="10"/>
+        <v>8.5080091590000295E-2</v>
+      </c>
+      <c r="P83" s="11">
+        <f t="shared" si="11"/>
+        <v>8.3699717660000061E-2</v>
+      </c>
+      <c r="Q83" s="11">
+        <f t="shared" si="12"/>
+        <v>7.0462086595999951E-2</v>
+      </c>
+      <c r="R83" s="11">
         <f t="shared" si="13"/>
-        <v>2.7312549184000057E-2</v>
-      </c>
-      <c r="F83" s="11">
-        <f t="shared" si="0"/>
-        <v>3.4058408128000206E-2</v>
-      </c>
-      <c r="G83" s="11">
-        <f t="shared" si="1"/>
-        <v>3.0564967560000156E-2</v>
-      </c>
-      <c r="H83" s="11">
-        <f t="shared" si="2"/>
-        <v>1.3517417879999938E-2</v>
-      </c>
-      <c r="I83" s="11">
-        <f t="shared" si="3"/>
-        <v>1.1213286160000058E-2</v>
-      </c>
-      <c r="J83" s="11">
-        <f t="shared" si="4"/>
-        <v>8.9852006320000122E-2</v>
-      </c>
-      <c r="K83" s="11">
-        <f t="shared" si="5"/>
-        <v>0.14855648964000001</v>
-      </c>
-      <c r="L83" s="11">
-        <f t="shared" si="6"/>
-        <v>0.16824147801999989</v>
-      </c>
-      <c r="M83" s="11">
-        <f t="shared" si="7"/>
-        <v>0.10437184679799993</v>
-      </c>
-      <c r="N83" s="11">
-        <f t="shared" si="8"/>
-        <v>8.2234048994999975E-2</v>
-      </c>
-      <c r="O83" s="11">
-        <f t="shared" si="9"/>
-        <v>8.5080091590000295E-2</v>
-      </c>
-      <c r="P83" s="11">
-        <f t="shared" si="10"/>
-        <v>8.3699717660000061E-2</v>
-      </c>
-      <c r="Q83" s="11">
-        <f t="shared" si="11"/>
-        <v>7.0462086595999951E-2</v>
-      </c>
-      <c r="R83" s="11">
-        <f t="shared" si="12"/>
         <v>6.0583137865999781E-2</v>
       </c>
     </row>
@@ -35511,59 +36538,59 @@
         <v>90</v>
       </c>
       <c r="E84" s="11">
+        <f t="shared" si="0"/>
+        <v>1.5547748768000025E-2</v>
+      </c>
+      <c r="F84" s="11">
+        <f t="shared" si="1"/>
+        <v>3.6045415160000038E-2</v>
+      </c>
+      <c r="G84" s="11">
+        <f t="shared" si="2"/>
+        <v>4.6270566799999857E-2</v>
+      </c>
+      <c r="H84" s="11">
+        <f t="shared" si="3"/>
+        <v>3.9651219599999843E-2</v>
+      </c>
+      <c r="I84" s="11">
+        <f t="shared" si="4"/>
+        <v>3.9345739319999851E-2</v>
+      </c>
+      <c r="J84" s="11">
+        <f t="shared" si="5"/>
+        <v>8.6644691524000006E-2</v>
+      </c>
+      <c r="K84" s="11">
+        <f t="shared" si="6"/>
+        <v>0.14220929274199978</v>
+      </c>
+      <c r="L84" s="11">
+        <f t="shared" si="7"/>
+        <v>0.14500690539200001</v>
+      </c>
+      <c r="M84" s="11">
+        <f t="shared" si="8"/>
+        <v>9.1167472016000284E-2</v>
+      </c>
+      <c r="N84" s="11">
+        <f t="shared" si="9"/>
+        <v>5.7707481391999993E-2</v>
+      </c>
+      <c r="O84" s="11">
+        <f t="shared" si="10"/>
+        <v>5.7604108885999983E-2</v>
+      </c>
+      <c r="P84" s="11">
+        <f t="shared" si="11"/>
+        <v>6.7663555477999848E-2</v>
+      </c>
+      <c r="Q84" s="11">
+        <f t="shared" si="12"/>
+        <v>6.1096204960999989E-2</v>
+      </c>
+      <c r="R84" s="11">
         <f t="shared" si="13"/>
-        <v>1.5547748768000025E-2</v>
-      </c>
-      <c r="F84" s="11">
-        <f t="shared" si="0"/>
-        <v>3.6045415160000038E-2</v>
-      </c>
-      <c r="G84" s="11">
-        <f t="shared" si="1"/>
-        <v>4.6270566799999857E-2</v>
-      </c>
-      <c r="H84" s="11">
-        <f t="shared" si="2"/>
-        <v>3.9651219599999843E-2</v>
-      </c>
-      <c r="I84" s="11">
-        <f t="shared" si="3"/>
-        <v>3.9345739319999851E-2</v>
-      </c>
-      <c r="J84" s="11">
-        <f t="shared" si="4"/>
-        <v>8.6644691524000006E-2</v>
-      </c>
-      <c r="K84" s="11">
-        <f t="shared" si="5"/>
-        <v>0.14220929274199978</v>
-      </c>
-      <c r="L84" s="11">
-        <f t="shared" si="6"/>
-        <v>0.14500690539200001</v>
-      </c>
-      <c r="M84" s="11">
-        <f t="shared" si="7"/>
-        <v>9.1167472016000284E-2</v>
-      </c>
-      <c r="N84" s="11">
-        <f t="shared" si="8"/>
-        <v>5.7707481391999993E-2</v>
-      </c>
-      <c r="O84" s="11">
-        <f t="shared" si="9"/>
-        <v>5.7604108885999983E-2</v>
-      </c>
-      <c r="P84" s="11">
-        <f t="shared" si="10"/>
-        <v>6.7663555477999848E-2</v>
-      </c>
-      <c r="Q84" s="11">
-        <f t="shared" si="11"/>
-        <v>6.1096204960999989E-2</v>
-      </c>
-      <c r="R84" s="11">
-        <f t="shared" si="12"/>
         <v>5.6325368735000048E-2</v>
       </c>
     </row>
@@ -35575,59 +36602,59 @@
         <v>90</v>
       </c>
       <c r="E85" s="11">
+        <f t="shared" si="0"/>
+        <v>1.4312327232000044E-2</v>
+      </c>
+      <c r="F85" s="11">
+        <f t="shared" si="1"/>
+        <v>2.5249401047999998E-2</v>
+      </c>
+      <c r="G85" s="11">
+        <f t="shared" si="2"/>
+        <v>3.2635628471999967E-2</v>
+      </c>
+      <c r="H85" s="11">
+        <f t="shared" si="3"/>
+        <v>1.7349400871999876E-2</v>
+      </c>
+      <c r="I85" s="11">
+        <f t="shared" si="4"/>
+        <v>2.4484111210000048E-2</v>
+      </c>
+      <c r="J85" s="11">
+        <f t="shared" si="5"/>
+        <v>0.10682144937499993</v>
+      </c>
+      <c r="K85" s="11">
+        <f t="shared" si="6"/>
+        <v>0.17423078937499992</v>
+      </c>
+      <c r="L85" s="11">
+        <f t="shared" si="7"/>
+        <v>0.16421037949999984</v>
+      </c>
+      <c r="M85" s="11">
+        <f t="shared" si="8"/>
+        <v>8.798805396399989E-2</v>
+      </c>
+      <c r="N85" s="11">
+        <f t="shared" si="9"/>
+        <v>5.7991593595999813E-2</v>
+      </c>
+      <c r="O85" s="11">
+        <f t="shared" si="10"/>
+        <v>7.4005910357000104E-2</v>
+      </c>
+      <c r="P85" s="11">
+        <f t="shared" si="11"/>
+        <v>7.2737773889000046E-2</v>
+      </c>
+      <c r="Q85" s="11">
+        <f t="shared" si="12"/>
+        <v>6.0030325746999846E-2</v>
+      </c>
+      <c r="R85" s="11">
         <f t="shared" si="13"/>
-        <v>1.4312327232000044E-2</v>
-      </c>
-      <c r="F85" s="11">
-        <f t="shared" si="0"/>
-        <v>2.5249401047999998E-2</v>
-      </c>
-      <c r="G85" s="11">
-        <f t="shared" si="1"/>
-        <v>3.2635628471999967E-2</v>
-      </c>
-      <c r="H85" s="11">
-        <f t="shared" si="2"/>
-        <v>1.7349400871999876E-2</v>
-      </c>
-      <c r="I85" s="11">
-        <f t="shared" si="3"/>
-        <v>2.4484111210000048E-2</v>
-      </c>
-      <c r="J85" s="11">
-        <f t="shared" si="4"/>
-        <v>0.10682144937499993</v>
-      </c>
-      <c r="K85" s="11">
-        <f t="shared" si="5"/>
-        <v>0.17423078937499992</v>
-      </c>
-      <c r="L85" s="11">
-        <f t="shared" si="6"/>
-        <v>0.16421037949999984</v>
-      </c>
-      <c r="M85" s="11">
-        <f t="shared" si="7"/>
-        <v>8.798805396399989E-2</v>
-      </c>
-      <c r="N85" s="11">
-        <f t="shared" si="8"/>
-        <v>5.7991593595999813E-2</v>
-      </c>
-      <c r="O85" s="11">
-        <f t="shared" si="9"/>
-        <v>7.4005910357000104E-2</v>
-      </c>
-      <c r="P85" s="11">
-        <f t="shared" si="10"/>
-        <v>7.2737773889000046E-2</v>
-      </c>
-      <c r="Q85" s="11">
-        <f t="shared" si="11"/>
-        <v>6.0030325746999846E-2</v>
-      </c>
-      <c r="R85" s="11">
-        <f t="shared" si="12"/>
         <v>5.1972401040999872E-2</v>
       </c>
     </row>
@@ -43534,12 +44561,6 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="4" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
